--- a/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
@@ -1618,6 +1618,87 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1640,87 +1721,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2025,28 +2025,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="16.5" thickBot="1">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="158" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="133"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="159"/>
+      <c r="T1" s="160"/>
     </row>
     <row r="2" spans="1:36" s="95" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="118" t="s">
@@ -2130,7 +2130,7 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="153" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="62" t="s">
@@ -2191,7 +2191,7 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="127"/>
+      <c r="B4" s="154"/>
       <c r="C4" s="65" t="s">
         <v>27</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="127"/>
+      <c r="B5" s="154"/>
       <c r="C5" s="65" t="s">
         <v>34</v>
       </c>
@@ -2309,7 +2309,7 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="127"/>
+      <c r="B6" s="154"/>
       <c r="C6" s="68" t="s">
         <v>41</v>
       </c>
@@ -2368,7 +2368,7 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="127"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="68" t="s">
         <v>48</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="127"/>
+      <c r="B8" s="154"/>
       <c r="C8" s="68" t="s">
         <v>55</v>
       </c>
@@ -2486,7 +2486,7 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="127"/>
+      <c r="B9" s="154"/>
       <c r="C9" s="68" t="s">
         <v>63</v>
       </c>
@@ -2546,7 +2546,7 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="127"/>
+      <c r="B10" s="154"/>
       <c r="C10" s="68" t="s">
         <v>67</v>
       </c>
@@ -2606,7 +2606,7 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="127"/>
+      <c r="B11" s="154"/>
       <c r="C11" s="68" t="s">
         <v>72</v>
       </c>
@@ -2666,7 +2666,7 @@
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="128"/>
+      <c r="B12" s="155"/>
       <c r="C12" s="74" t="s">
         <v>79</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="126" t="s">
+      <c r="B13" s="153" t="s">
         <v>86</v>
       </c>
       <c r="C13" s="80" t="s">
@@ -2788,7 +2788,7 @@
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="128"/>
+      <c r="B14" s="155"/>
       <c r="C14" s="74" t="s">
         <v>94</v>
       </c>
@@ -2941,7 +2941,7 @@
       <c r="L16" s="111">
         <v>1</v>
       </c>
-      <c r="M16" s="134">
+      <c r="M16" s="126">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2951,20 +2951,20 @@
       <c r="O16" s="113">
         <v>0.97699999999999998</v>
       </c>
-      <c r="P16" s="135">
+      <c r="P16" s="127">
         <f t="shared" si="1"/>
         <v>0.97699999999999998</v>
       </c>
-      <c r="Q16" s="135">
+      <c r="Q16" s="127">
         <v>0.97699999999999998</v>
       </c>
-      <c r="R16" s="136">
+      <c r="R16" s="128">
         <f t="shared" si="2"/>
         <v>6.8389999999999995</v>
       </c>
       <c r="S16" s="111"/>
       <c r="T16" s="123">
-        <v>0.97699999999999998</v>
+        <v>2.54</v>
       </c>
       <c r="U16" s="50"/>
     </row>
@@ -2972,7 +2972,7 @@
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="153" t="s">
         <v>111</v>
       </c>
       <c r="C17" s="85" t="s">
@@ -3034,7 +3034,7 @@
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="127"/>
+      <c r="B18" s="154"/>
       <c r="C18" s="87" t="s">
         <v>118</v>
       </c>
@@ -3094,7 +3094,7 @@
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="127"/>
+      <c r="B19" s="154"/>
       <c r="C19" s="87" t="s">
         <v>123</v>
       </c>
@@ -3154,7 +3154,7 @@
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="127"/>
+      <c r="B20" s="154"/>
       <c r="C20" s="87" t="s">
         <v>128</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="127"/>
+      <c r="B21" s="154"/>
       <c r="C21" s="87" t="s">
         <v>135</v>
       </c>
@@ -3274,7 +3274,7 @@
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="127"/>
+      <c r="B22" s="154"/>
       <c r="C22" s="87" t="s">
         <v>142</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="128"/>
+      <c r="B23" s="155"/>
       <c r="C23" s="89" t="s">
         <v>148</v>
       </c>
@@ -3394,65 +3394,65 @@
       <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="126" t="s">
+      <c r="B24" s="153" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="137" t="s">
+      <c r="C24" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="138" t="s">
+      <c r="D24" s="130" t="s">
         <v>155</v>
       </c>
-      <c r="E24" s="138" t="s">
+      <c r="E24" s="130" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="138" t="s">
+      <c r="F24" s="130" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="139" t="s">
+      <c r="G24" s="131" t="s">
         <v>158</v>
       </c>
-      <c r="H24" s="139" t="s">
+      <c r="H24" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="138" t="s">
+      <c r="I24" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="J24" s="139" t="s">
+      <c r="J24" s="131" t="s">
         <v>93</v>
       </c>
-      <c r="K24" s="140">
+      <c r="K24" s="132">
         <v>10</v>
       </c>
-      <c r="L24" s="140">
+      <c r="L24" s="132">
         <v>1</v>
       </c>
-      <c r="M24" s="141">
+      <c r="M24" s="133">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="142" t="s">
+      <c r="N24" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="O24" s="143">
+      <c r="O24" s="135">
         <v>1.2</v>
       </c>
-      <c r="P24" s="143">
+      <c r="P24" s="135">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="Q24" s="143">
+      <c r="Q24" s="135">
         <v>1.2</v>
       </c>
-      <c r="R24" s="144">
+      <c r="R24" s="136">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="S24" s="145" t="s">
+      <c r="S24" s="137" t="s">
         <v>212</v>
       </c>
-      <c r="T24" s="146">
-        <v>2.8347000000000002</v>
+      <c r="T24" s="138">
+        <v>4.7619999999999996</v>
       </c>
       <c r="U24" s="50"/>
     </row>
@@ -3460,7 +3460,7 @@
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="127"/>
+      <c r="B25" s="154"/>
       <c r="C25" s="87" t="s">
         <v>160</v>
       </c>
@@ -3520,7 +3520,7 @@
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="128"/>
+      <c r="B26" s="155"/>
       <c r="C26" s="89" t="s">
         <v>166</v>
       </c>
@@ -3580,191 +3580,191 @@
       <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="153" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="137" t="s">
+      <c r="C27" s="129" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="138" t="s">
+      <c r="D27" s="130" t="s">
         <v>174</v>
       </c>
-      <c r="E27" s="138" t="s">
+      <c r="E27" s="130" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="138" t="s">
+      <c r="F27" s="130" t="s">
         <v>175</v>
       </c>
-      <c r="G27" s="138" t="s">
+      <c r="G27" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="H27" s="138" t="s">
+      <c r="H27" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="138" t="s">
+      <c r="I27" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="J27" s="138" t="s">
+      <c r="J27" s="130" t="s">
         <v>93</v>
       </c>
-      <c r="K27" s="141">
+      <c r="K27" s="133">
         <v>100</v>
       </c>
-      <c r="L27" s="141">
+      <c r="L27" s="133">
         <v>1</v>
       </c>
-      <c r="M27" s="141">
+      <c r="M27" s="133">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N27" s="147" t="s">
+      <c r="N27" s="139" t="s">
         <v>177</v>
       </c>
-      <c r="O27" s="143">
+      <c r="O27" s="135">
         <v>36.9</v>
       </c>
-      <c r="P27" s="143">
+      <c r="P27" s="135">
         <f t="shared" si="1"/>
         <v>36.9</v>
       </c>
-      <c r="Q27" s="143">
+      <c r="Q27" s="135">
         <v>0.36899999999999999</v>
       </c>
-      <c r="R27" s="144">
+      <c r="R27" s="136">
         <f t="shared" si="2"/>
         <v>36.9</v>
       </c>
-      <c r="S27" s="148" t="s">
+      <c r="S27" s="140" t="s">
         <v>213</v>
       </c>
-      <c r="T27" s="146"/>
+      <c r="T27" s="138"/>
       <c r="U27" s="50"/>
     </row>
     <row r="28" spans="1:21" ht="15.75" thickBot="1">
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="127"/>
-      <c r="C28" s="149" t="s">
+      <c r="B28" s="154"/>
+      <c r="C28" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="150" t="s">
+      <c r="D28" s="142" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="150" t="s">
+      <c r="E28" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="150" t="s">
+      <c r="F28" s="142" t="s">
         <v>180</v>
       </c>
-      <c r="G28" s="150" t="s">
+      <c r="G28" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="H28" s="150" t="s">
+      <c r="H28" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="150" t="s">
+      <c r="I28" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="J28" s="151" t="s">
+      <c r="J28" s="143" t="s">
         <v>215</v>
       </c>
-      <c r="K28" s="152">
+      <c r="K28" s="144">
         <v>12</v>
       </c>
-      <c r="L28" s="153">
+      <c r="L28" s="145">
         <v>2</v>
       </c>
-      <c r="M28" s="153">
+      <c r="M28" s="145">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28" s="154" t="s">
+      <c r="N28" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="O28" s="155">
+      <c r="O28" s="147">
         <v>0.75</v>
       </c>
-      <c r="P28" s="156">
+      <c r="P28" s="148">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="Q28" s="155">
+      <c r="Q28" s="147">
         <v>0.75</v>
       </c>
-      <c r="R28" s="157">
+      <c r="R28" s="149">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="S28" s="158"/>
-      <c r="T28" s="159"/>
+      <c r="S28" s="150"/>
+      <c r="T28" s="151"/>
       <c r="U28" s="50"/>
     </row>
     <row r="29" spans="1:21" ht="15.75" thickBot="1">
       <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="127"/>
-      <c r="C29" s="149" t="s">
+      <c r="B29" s="154"/>
+      <c r="C29" s="141" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="150" t="s">
+      <c r="D29" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="E29" s="150" t="s">
+      <c r="E29" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="150" t="s">
+      <c r="F29" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="G29" s="150" t="s">
+      <c r="G29" s="142" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="150" t="s">
+      <c r="H29" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="150" t="s">
+      <c r="I29" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="J29" s="151" t="s">
+      <c r="J29" s="143" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="152">
+      <c r="K29" s="144">
         <v>10</v>
       </c>
-      <c r="L29" s="153">
+      <c r="L29" s="145">
         <v>1</v>
       </c>
-      <c r="M29" s="153">
+      <c r="M29" s="145">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N29" s="154" t="s">
+      <c r="N29" s="146" t="s">
         <v>177</v>
       </c>
-      <c r="O29" s="160">
+      <c r="O29" s="152">
         <v>0.55300000000000005</v>
       </c>
-      <c r="P29" s="156">
+      <c r="P29" s="148">
         <f t="shared" si="1"/>
         <v>0.55300000000000005</v>
       </c>
-      <c r="Q29" s="156">
+      <c r="Q29" s="148">
         <v>0.55300000000000005</v>
       </c>
-      <c r="R29" s="157">
+      <c r="R29" s="149">
         <f t="shared" si="2"/>
         <v>5.53</v>
       </c>
-      <c r="S29" s="158"/>
-      <c r="T29" s="159"/>
+      <c r="S29" s="150"/>
+      <c r="T29" s="151"/>
       <c r="U29" s="50"/>
     </row>
     <row r="30" spans="1:21" ht="15.75" thickBot="1">
       <c r="A30" s="2">
         <v>28</v>
       </c>
-      <c r="B30" s="127"/>
+      <c r="B30" s="154"/>
       <c r="C30" s="87" t="s">
         <v>186</v>
       </c>
@@ -3824,7 +3824,7 @@
       <c r="A31" s="2">
         <v>29</v>
       </c>
-      <c r="B31" s="127"/>
+      <c r="B31" s="154"/>
       <c r="C31" s="87" t="s">
         <v>192</v>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="127"/>
+      <c r="B32" s="154"/>
       <c r="C32" s="91" t="s">
         <v>198</v>
       </c>
@@ -3924,7 +3924,7 @@
       <c r="A33" s="102">
         <v>31</v>
       </c>
-      <c r="B33" s="128"/>
+      <c r="B33" s="155"/>
       <c r="C33" s="93" t="s">
         <v>202</v>
       </c>
@@ -3971,11 +3971,11 @@
       <c r="I34" s="22"/>
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
-      <c r="L34" s="129" t="s">
+      <c r="L34" s="156" t="s">
         <v>205</v>
       </c>
-      <c r="M34" s="129"/>
-      <c r="N34" s="129"/>
+      <c r="M34" s="156"/>
+      <c r="N34" s="156"/>
       <c r="P34" s="125">
         <f>SUM(P3:P31)</f>
         <v>43.337799999999994</v>
@@ -3999,11 +3999,11 @@
       <c r="I35" s="22"/>
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
-      <c r="L35" s="130" t="s">
+      <c r="L35" s="157" t="s">
         <v>206</v>
       </c>
-      <c r="M35" s="130"/>
-      <c r="N35" s="130"/>
+      <c r="M35" s="157"/>
+      <c r="N35" s="157"/>
       <c r="R35" s="48">
         <f>R34/5</f>
         <v>17.850959999999997</v>

--- a/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9795"/>
+    <workbookView windowWidth="24000" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="214">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -60,12 +55,21 @@
     <t>Quantity (Per Board)</t>
   </si>
   <si>
+    <t>Quantity 5</t>
+  </si>
+  <si>
     <t>Link</t>
   </si>
   <si>
     <t>Unit Cost(1)</t>
   </si>
   <si>
+    <t>Total Cost (1)</t>
+  </si>
+  <si>
+    <t>Unit Cost(5)</t>
+  </si>
+  <si>
     <t>MOQ Total</t>
   </si>
   <si>
@@ -94,6 +98,9 @@
   </si>
   <si>
     <t>C113803</t>
+  </si>
+  <si>
+    <t>------------</t>
   </si>
   <si>
     <t>0.1uF</t>
@@ -207,9 +214,6 @@
     <t>C487322</t>
   </si>
   <si>
-    <t>------------</t>
-  </si>
-  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -226,6 +230,9 @@
   </si>
   <si>
     <t>CAP ALUM 10uF 25V SMD</t>
+  </si>
+  <si>
+    <t>C1</t>
   </si>
   <si>
     <t>RVT1E100M0405</t>
@@ -361,6 +368,9 @@
     <t xml:space="preserve">Panasonic </t>
   </si>
   <si>
+    <t>Custom Supplier</t>
+  </si>
+  <si>
     <t>Resistor</t>
   </si>
   <si>
@@ -512,6 +522,9 @@
     <t>Alibaba</t>
   </si>
   <si>
+    <t>MOQ=10</t>
+  </si>
+  <si>
     <t>2A 40V SOIC-8_EP_150mil DC-DC Converters ROHS</t>
   </si>
   <si>
@@ -550,6 +563,9 @@
     <t>C92102</t>
   </si>
   <si>
+    <t>---</t>
+  </si>
+  <si>
     <t>Connector</t>
   </si>
   <si>
@@ -568,7 +584,10 @@
     <t>Aliexpress</t>
   </si>
   <si>
-    <t>10/100 BASE-TX RJ45 WITH LEDS_x000D_
+    <t>MOQ=100</t>
+  </si>
+  <si>
+    <t>10/100 BASE-TX RJ45 WITH LEDS
 INTEGRATED MAGNETICS CONNECTOR</t>
   </si>
   <si>
@@ -581,6 +600,9 @@
     <t>SAK ELECTRONICS CO.,LTD</t>
   </si>
   <si>
+    <t>----</t>
+  </si>
+  <si>
     <t>Local Supplier</t>
   </si>
   <si>
@@ -593,22 +615,16 @@
     <t>1125N1202SNM</t>
   </si>
   <si>
-    <t>2.54mm Straight 1 4 Header TH,P=2.54mm Pin Headers ROHS</t>
+    <t>2.54mm Black Brass Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>HDR1X4</t>
-  </si>
-  <si>
-    <t>MTP125-1104S1</t>
-  </si>
-  <si>
-    <t>MINTRON</t>
-  </si>
-  <si>
-    <t>C358686</t>
+    <t>C37208</t>
+  </si>
+  <si>
+    <t>BOOMELEC</t>
   </si>
   <si>
     <t>CONN HEADER VERT 2POS 2.54MM</t>
@@ -654,49 +670,33 @@
   </si>
   <si>
     <t>Single Board Cost</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Quantity 5</t>
-  </si>
-  <si>
-    <t>Total Cost (1)</t>
-  </si>
-  <si>
-    <t>Unit Cost(5)</t>
-  </si>
-  <si>
-    <t>Custom Supplier</t>
-  </si>
-  <si>
-    <t>MOQ=10</t>
-  </si>
-  <si>
-    <t>MOQ=100</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
-    <t>----</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -718,8 +718,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -761,6 +777,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -769,15 +791,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF24292F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -800,44 +855,140 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <strike/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -845,11 +996,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -882,7 +1033,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,8 +1043,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1085,6 +1422,54 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="medium">
         <color auto="1"/>
@@ -1106,17 +1491,6 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -1168,32 +1542,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1224,38 +1572,291 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1263,479 +1864,578 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="6" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="4" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="6" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="22" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="19" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="23" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="22" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
+    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
+    <cellStyle name="Note" xfId="12" builtinId="10"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="Title" xfId="16" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
+    <cellStyle name="Input" xfId="21" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
+    <cellStyle name="Good" xfId="23" builtinId="26"/>
+    <cellStyle name="Output" xfId="24" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bad" xfId="29" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1993,121 +2693,120 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AJ50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.14285714285714" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="62.1809523809524" customWidth="1"/>
+    <col min="4" max="4" width="34.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="15.2857142857143" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.5714285714286" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" customWidth="1"/>
-    <col min="20" max="20" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5714285714286" customWidth="1"/>
+    <col min="12" max="12" width="21.8571428571429" customWidth="1"/>
+    <col min="13" max="13" width="14.1428571428571" customWidth="1"/>
+    <col min="14" max="14" width="16.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="12.7142857142857" customWidth="1"/>
+    <col min="16" max="17" width="14.2857142857143" customWidth="1"/>
+    <col min="18" max="18" width="13.4285714285714" customWidth="1"/>
+    <col min="19" max="19" width="14.1428571428571" customWidth="1"/>
+    <col min="20" max="20" width="50.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="16.5" thickBot="1">
-      <c r="A1" s="158" t="s">
+    <row r="1" ht="16.5" spans="1:20">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
-      <c r="O1" s="159"/>
-      <c r="P1" s="159"/>
-      <c r="Q1" s="159"/>
-      <c r="R1" s="159"/>
-      <c r="S1" s="159"/>
-      <c r="T1" s="160"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="106"/>
     </row>
-    <row r="2" spans="1:36" s="95" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A2" s="118" t="s">
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:36">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="119" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="98" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="98" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="98" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="98" t="s">
+      <c r="K2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="98" t="s">
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="98" t="s">
-        <v>208</v>
-      </c>
-      <c r="N2" s="120" t="s">
+      <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="100" t="s">
+      <c r="N2" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="100" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q2" s="100" t="s">
-        <v>210</v>
-      </c>
-      <c r="R2" s="98" t="s">
+      <c r="O2" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="98" t="s">
+      <c r="P2" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="98" t="s">
+      <c r="Q2" s="56" t="s">
         <v>17</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="U2"/>
       <c r="V2"/>
@@ -2126,1975 +2825,1975 @@
       <c r="AI2"/>
       <c r="AJ2"/>
     </row>
-    <row r="3" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A3" s="2">
+    <row r="3" ht="15.75" spans="1:20">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="153" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="63" t="s">
+      <c r="B3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="C3" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="D3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="63" t="s">
+      <c r="F3" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="17">
+      <c r="G3" s="142" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="33">
         <v>50</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="12">
         <v>4</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="33">
         <f>L3*5</f>
         <v>20</v>
       </c>
-      <c r="N3" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="36">
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="P3" s="36">
+      <c r="N3" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="58">
+        <v>0.0082</v>
+      </c>
+      <c r="P3" s="58">
         <f>O3*L3</f>
-        <v>3.2800000000000003E-2</v>
-      </c>
-      <c r="Q3" s="36">
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="R3" s="25">
+        <v>0.0328</v>
+      </c>
+      <c r="Q3" s="58">
+        <v>0.0082</v>
+      </c>
+      <c r="R3" s="107">
         <f>Q3*K3</f>
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="S3" s="17"/>
-      <c r="T3" s="49"/>
+        <v>0.41</v>
+      </c>
+      <c r="S3" s="33"/>
+      <c r="T3" s="108"/>
     </row>
-    <row r="4" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A4" s="2">
+    <row r="4" ht="15.75" spans="1:20">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="67" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="145" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="146" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="147" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="148" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="10">
+      <c r="J4" s="147" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="23">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="18">
         <v>1</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="23">
         <f t="shared" ref="M4:M33" si="0">L4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="29">
-        <v>6.8199999999999997E-2</v>
-      </c>
-      <c r="P4" s="29">
+      <c r="N4" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="60">
+        <v>0.0682</v>
+      </c>
+      <c r="P4" s="60">
         <f t="shared" ref="P4:P31" si="1">O4*L4</f>
-        <v>6.8199999999999997E-2</v>
-      </c>
-      <c r="Q4" s="29">
-        <v>6.8199999999999997E-2</v>
-      </c>
-      <c r="R4" s="27">
+        <v>0.0682</v>
+      </c>
+      <c r="Q4" s="60">
+        <v>0.0682</v>
+      </c>
+      <c r="R4" s="109">
         <f t="shared" ref="R4:R31" si="2">Q4*K4</f>
-        <v>0.68199999999999994</v>
-      </c>
-      <c r="S4" s="10"/>
-      <c r="T4" s="51"/>
+        <v>0.682</v>
+      </c>
+      <c r="S4" s="23"/>
+      <c r="T4" s="110"/>
     </row>
-    <row r="5" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A5" s="2">
+    <row r="5" ht="15.75" spans="1:20">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="97" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="9" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="D5" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="66" t="s">
+      <c r="E5" s="147" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="10">
+      <c r="G5" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="147" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="23">
         <v>100</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="18">
         <v>8</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="23">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N5" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="29">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="P5" s="29">
+      <c r="N5" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="60">
+        <v>0.0031</v>
+      </c>
+      <c r="P5" s="60">
         <f t="shared" si="1"/>
-        <v>2.4799999999999999E-2</v>
-      </c>
-      <c r="Q5" s="29">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="R5" s="27">
+        <v>0.0248</v>
+      </c>
+      <c r="Q5" s="60">
+        <v>0.0031</v>
+      </c>
+      <c r="R5" s="109">
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="51"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="110"/>
     </row>
-    <row r="6" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A6" s="2">
+    <row r="6" ht="15.75" spans="1:20">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
-      <c r="B6" s="154"/>
-      <c r="C6" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="97" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="12" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="67" t="s">
+      <c r="D6" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="E6" s="151" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="10">
+      <c r="G6" s="152" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="146" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="11">
+      <c r="J6" s="151" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="23">
+        <v>50</v>
+      </c>
+      <c r="L6" s="24">
         <v>3</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="23">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N6" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="29">
-        <v>5.3E-3</v>
-      </c>
-      <c r="P6" s="29">
+      <c r="N6" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="60">
+        <v>0.0053</v>
+      </c>
+      <c r="P6" s="60">
         <f t="shared" si="1"/>
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="Q6" s="29">
-        <v>5.3E-3</v>
-      </c>
-      <c r="R6" s="27">
+        <v>0.0159</v>
+      </c>
+      <c r="Q6" s="60">
+        <v>0.0053</v>
+      </c>
+      <c r="R6" s="109">
         <f t="shared" si="2"/>
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="51"/>
+        <v>0.265</v>
+      </c>
+      <c r="S6" s="23"/>
+      <c r="T6" s="110"/>
     </row>
-    <row r="7" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A7" s="2">
+    <row r="7" ht="15.75" spans="1:20">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="154"/>
-      <c r="C7" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="97" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="12" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="D7" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="69" t="s">
+      <c r="E7" s="151" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="10">
+      <c r="G7" s="152" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="151" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="23">
         <v>10</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="24">
         <v>1</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N7" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="30">
-        <v>4.0300000000000002E-2</v>
-      </c>
-      <c r="P7" s="29">
+      <c r="N7" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="63">
+        <v>0.0403</v>
+      </c>
+      <c r="P7" s="60">
         <f t="shared" si="1"/>
-        <v>4.0300000000000002E-2</v>
-      </c>
-      <c r="Q7" s="29">
-        <v>4.0300000000000002E-2</v>
-      </c>
-      <c r="R7" s="27">
+        <v>0.0403</v>
+      </c>
+      <c r="Q7" s="60">
+        <v>0.0403</v>
+      </c>
+      <c r="R7" s="109">
         <f t="shared" si="2"/>
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="S7" s="10"/>
-      <c r="T7" s="51"/>
+        <v>0.403</v>
+      </c>
+      <c r="S7" s="23"/>
+      <c r="T7" s="110"/>
     </row>
-    <row r="8" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A8" s="2">
+    <row r="8" ht="15.75" spans="1:20">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
-      <c r="B8" s="154"/>
-      <c r="C8" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="67" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="70" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="D8" s="146" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="72" t="s">
+      <c r="E8" s="151" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="69" t="s">
+      <c r="F8" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="10">
+      <c r="G8" s="152" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="151" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="23">
         <v>10</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="64">
         <v>1</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="32">
-        <v>7.5899999999999995E-2</v>
-      </c>
-      <c r="P8" s="29">
+      <c r="N8" s="154" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="66">
+        <v>0.0759</v>
+      </c>
+      <c r="P8" s="60">
         <f t="shared" si="1"/>
-        <v>7.5899999999999995E-2</v>
-      </c>
-      <c r="Q8" s="29">
-        <v>7.5899999999999995E-2</v>
-      </c>
-      <c r="R8" s="27">
+        <v>0.0759</v>
+      </c>
+      <c r="Q8" s="60">
+        <v>0.0759</v>
+      </c>
+      <c r="R8" s="109">
         <f t="shared" si="2"/>
-        <v>0.7589999999999999</v>
-      </c>
-      <c r="S8" s="52"/>
-      <c r="T8" s="51"/>
+        <v>0.759</v>
+      </c>
+      <c r="S8" s="111"/>
+      <c r="T8" s="110"/>
     </row>
-    <row r="9" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A9" s="2">
+    <row r="9" ht="15.75" spans="1:21">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="154"/>
-      <c r="C9" s="68" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="151" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="146" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="152" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="67" t="s">
+      <c r="H9" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="151" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="K9" s="10">
+      <c r="K9" s="23">
         <v>12</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="64">
         <v>2</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N9" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="32">
-        <v>0.18110000000000001</v>
-      </c>
-      <c r="P9" s="29">
+      <c r="N9" s="154" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="66">
+        <v>0.1811</v>
+      </c>
+      <c r="P9" s="60">
         <f t="shared" si="1"/>
-        <v>0.36220000000000002</v>
-      </c>
-      <c r="Q9" s="29">
-        <v>0.18110000000000001</v>
-      </c>
-      <c r="R9" s="27">
+        <v>0.3622</v>
+      </c>
+      <c r="Q9" s="60">
+        <v>0.1811</v>
+      </c>
+      <c r="R9" s="109">
         <f t="shared" si="2"/>
         <v>2.1732</v>
       </c>
-      <c r="S9" s="52"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="50"/>
+      <c r="S9" s="111"/>
+      <c r="T9" s="110"/>
+      <c r="U9" s="112"/>
     </row>
-    <row r="10" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A10" s="2">
+    <row r="10" ht="15.75" spans="1:21">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="154"/>
-      <c r="C10" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="D10" s="146" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="151" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="10">
+      <c r="F10" s="146" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="151" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="23">
         <v>20</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="24">
         <v>1</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N10" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="29">
-        <v>3.5200000000000002E-2</v>
-      </c>
-      <c r="P10" s="29">
+      <c r="N10" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="60">
+        <v>0.0352</v>
+      </c>
+      <c r="P10" s="60">
         <f t="shared" si="1"/>
-        <v>3.5200000000000002E-2</v>
-      </c>
-      <c r="Q10" s="29">
-        <v>3.5200000000000002E-2</v>
-      </c>
-      <c r="R10" s="27">
+        <v>0.0352</v>
+      </c>
+      <c r="Q10" s="60">
+        <v>0.0352</v>
+      </c>
+      <c r="R10" s="109">
         <f t="shared" si="2"/>
-        <v>0.70400000000000007</v>
-      </c>
-      <c r="S10" s="10"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="50"/>
+        <v>0.704</v>
+      </c>
+      <c r="S10" s="23"/>
+      <c r="T10" s="110"/>
+      <c r="U10" s="112"/>
     </row>
-    <row r="11" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A11" s="2">
+    <row r="11" ht="15.75" spans="1:21">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B11" s="154"/>
-      <c r="C11" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="70" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="D11" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" s="69" t="s">
+      <c r="E11" s="151" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="10">
+      <c r="F11" s="146" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="152" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="151" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="23">
         <v>10</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="24">
         <v>1</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N11" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="29">
-        <v>9.5799999999999996E-2</v>
-      </c>
-      <c r="P11" s="29">
+      <c r="N11" s="153" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="60">
+        <v>0.0958</v>
+      </c>
+      <c r="P11" s="60">
         <f t="shared" si="1"/>
-        <v>9.5799999999999996E-2</v>
-      </c>
-      <c r="Q11" s="29">
-        <v>9.5799999999999996E-2</v>
-      </c>
-      <c r="R11" s="27">
+        <v>0.0958</v>
+      </c>
+      <c r="Q11" s="60">
+        <v>0.0958</v>
+      </c>
+      <c r="R11" s="109">
         <f t="shared" si="2"/>
-        <v>0.95799999999999996</v>
-      </c>
-      <c r="S11" s="53"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="54"/>
+        <v>0.958</v>
+      </c>
+      <c r="S11" s="113"/>
+      <c r="T11" s="110"/>
+      <c r="U11" s="114"/>
     </row>
-    <row r="12" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A12" s="2">
+    <row r="12" ht="15.75" spans="1:21">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
-      <c r="B12" s="155"/>
-      <c r="C12" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="77" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="D12" s="156" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="78" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="75" t="s">
+      <c r="E12" s="157" t="s">
         <v>85</v>
       </c>
-      <c r="K12" s="13">
+      <c r="F12" s="156" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="158" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="159" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="157" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" s="29">
         <v>50</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="30">
         <v>1</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="33">
-        <v>1.47E-2</v>
-      </c>
-      <c r="P12" s="33">
+      <c r="N12" s="160" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="68">
+        <v>0.0147</v>
+      </c>
+      <c r="P12" s="68">
         <f t="shared" si="1"/>
-        <v>1.47E-2</v>
-      </c>
-      <c r="Q12" s="33">
-        <v>1.47E-2</v>
-      </c>
-      <c r="R12" s="34">
+        <v>0.0147</v>
+      </c>
+      <c r="Q12" s="68">
+        <v>0.0147</v>
+      </c>
+      <c r="R12" s="115">
         <f t="shared" si="2"/>
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="S12" s="13"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="50"/>
+        <v>0.735</v>
+      </c>
+      <c r="S12" s="29"/>
+      <c r="T12" s="116"/>
+      <c r="U12" s="112"/>
     </row>
-    <row r="13" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A13" s="2">
+    <row r="13" ht="15.75" spans="1:21">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
-      <c r="B13" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="81" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" s="64" t="s">
+      <c r="B13" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="C13" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="D13" s="143" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="83" t="s">
+      <c r="E13" s="162" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="17">
+      <c r="F13" s="143" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="162" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="163" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" s="33">
         <v>7</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="70">
         <v>1</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N13" s="84" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="36">
-        <v>0.31719999999999998</v>
-      </c>
-      <c r="P13" s="36">
+      <c r="N13" s="164" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="58">
+        <v>0.3172</v>
+      </c>
+      <c r="P13" s="58">
         <f t="shared" si="1"/>
-        <v>0.31719999999999998</v>
-      </c>
-      <c r="Q13" s="36">
-        <v>0.31719999999999998</v>
-      </c>
-      <c r="R13" s="25">
+        <v>0.3172</v>
+      </c>
+      <c r="Q13" s="58">
+        <v>0.3172</v>
+      </c>
+      <c r="R13" s="107">
         <f t="shared" si="2"/>
-        <v>2.2203999999999997</v>
-      </c>
-      <c r="S13" s="17"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="50"/>
+        <v>2.2204</v>
+      </c>
+      <c r="S13" s="33"/>
+      <c r="T13" s="108"/>
+      <c r="U13" s="112"/>
     </row>
-    <row r="14" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A14" s="2">
+    <row r="14" ht="15.75" spans="1:21">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
-      <c r="B14" s="155"/>
-      <c r="C14" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="76" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="75" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="76" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="155" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="156" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="157" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="156" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="157" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="159" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="159" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="158" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="78" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="K14" s="29">
         <v>20</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="72">
         <v>1</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="38">
-        <v>2.6599999999999999E-2</v>
-      </c>
-      <c r="P14" s="33">
+      <c r="N14" s="160" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="73">
+        <v>0.0266</v>
+      </c>
+      <c r="P14" s="68">
         <f t="shared" si="1"/>
-        <v>2.6599999999999999E-2</v>
-      </c>
-      <c r="Q14" s="33">
-        <v>2.6599999999999999E-2</v>
-      </c>
-      <c r="R14" s="34">
+        <v>0.0266</v>
+      </c>
+      <c r="Q14" s="68">
+        <v>0.0266</v>
+      </c>
+      <c r="R14" s="115">
         <f t="shared" si="2"/>
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="S14" s="56"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="50"/>
+        <v>0.532</v>
+      </c>
+      <c r="S14" s="117"/>
+      <c r="T14" s="116"/>
+      <c r="U14" s="112"/>
     </row>
-    <row r="15" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A15" s="2">
+    <row r="15" ht="15.75" spans="1:21">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
-      <c r="B15" s="121" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="109" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" s="103" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" s="103" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="103" t="s">
+      <c r="B15" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="C15" s="165" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="103" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="99" t="s">
-        <v>93</v>
-      </c>
-      <c r="K15" s="104">
+      <c r="D15" s="166" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="166" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="166" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="167" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="167" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="166" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="167" t="s">
+        <v>97</v>
+      </c>
+      <c r="K15" s="37">
         <v>7</v>
       </c>
-      <c r="L15" s="104">
+      <c r="L15" s="37">
         <v>1</v>
       </c>
-      <c r="M15" s="105">
+      <c r="M15" s="74">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N15" s="114" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="108">
+      <c r="N15" s="168" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="76">
         <v>0.2127</v>
       </c>
-      <c r="P15" s="101">
+      <c r="P15" s="77">
         <f t="shared" si="1"/>
         <v>0.2127</v>
       </c>
-      <c r="Q15" s="101">
+      <c r="Q15" s="77">
         <v>0.2127</v>
       </c>
-      <c r="R15" s="106">
+      <c r="R15" s="118">
         <f t="shared" si="2"/>
-        <v>1.4889000000000001</v>
-      </c>
-      <c r="S15" s="115"/>
-      <c r="T15" s="107">
+        <v>1.4889</v>
+      </c>
+      <c r="S15" s="119"/>
+      <c r="T15" s="120">
         <v>0.189</v>
       </c>
-      <c r="U15" s="50"/>
+      <c r="U15" s="112"/>
     </row>
-    <row r="16" spans="1:36" ht="15.75" thickBot="1">
-      <c r="A16" s="2">
+    <row r="16" ht="15.75" spans="1:21">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
-      <c r="B16" s="122" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="117" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="110" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="110" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="110" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="110" t="s">
+      <c r="B16" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="110" t="s">
-        <v>93</v>
-      </c>
-      <c r="K16" s="111">
+      <c r="C16" s="169" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="170" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="170" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="170" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="170" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="170" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="39">
         <v>7</v>
       </c>
-      <c r="L16" s="111">
+      <c r="L16" s="39">
         <v>1</v>
       </c>
-      <c r="M16" s="126">
+      <c r="M16" s="78">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N16" s="112" t="s">
-        <v>211</v>
-      </c>
-      <c r="O16" s="113">
-        <v>0.97699999999999998</v>
-      </c>
-      <c r="P16" s="127">
+      <c r="N16" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" s="80">
+        <v>0.977</v>
+      </c>
+      <c r="P16" s="81">
         <f t="shared" si="1"/>
-        <v>0.97699999999999998</v>
-      </c>
-      <c r="Q16" s="127">
-        <v>0.97699999999999998</v>
-      </c>
-      <c r="R16" s="128">
+        <v>0.977</v>
+      </c>
+      <c r="Q16" s="81">
+        <v>0.977</v>
+      </c>
+      <c r="R16" s="121">
         <f t="shared" si="2"/>
-        <v>6.8389999999999995</v>
-      </c>
-      <c r="S16" s="111"/>
-      <c r="T16" s="123">
+        <v>6.839</v>
+      </c>
+      <c r="S16" s="39"/>
+      <c r="T16" s="122">
         <v>2.54</v>
       </c>
-      <c r="U16" s="50"/>
+      <c r="U16" s="112"/>
     </row>
-    <row r="17" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A17" s="2">
+    <row r="17" ht="15.75" spans="1:21">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
-      <c r="B17" s="153" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="82" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="18" t="s">
+      <c r="B17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" s="64" t="s">
+      <c r="C17" s="171" t="s">
         <v>117</v>
       </c>
-      <c r="K17" s="4">
+      <c r="D17" s="143" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="143" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="143" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="144" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="143" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="K17" s="13">
         <v>100</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="13">
         <v>2</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N17" s="86" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="P17" s="36">
+      <c r="N17" s="172" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="83">
+        <v>0.0014</v>
+      </c>
+      <c r="P17" s="58">
         <f t="shared" si="1"/>
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q17" s="36">
-        <v>1.4E-3</v>
-      </c>
-      <c r="R17" s="25">
+        <v>0.0028</v>
+      </c>
+      <c r="Q17" s="58">
+        <v>0.0014</v>
+      </c>
+      <c r="R17" s="107">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="S17" s="4"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="50"/>
+        <v>0.14</v>
+      </c>
+      <c r="S17" s="13"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="112"/>
     </row>
-    <row r="18" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A18" s="2">
+    <row r="18" ht="15.75" spans="1:21">
+      <c r="A18" s="8">
         <v>16</v>
       </c>
-      <c r="B18" s="154"/>
-      <c r="C18" s="87" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="K18" s="7">
+      <c r="F18" s="146" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="146" t="s">
+        <v>127</v>
+      </c>
+      <c r="K18" s="17">
         <v>100</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="17">
         <v>2</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N18" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="40">
-        <v>1.4E-3</v>
-      </c>
-      <c r="P18" s="29">
+      <c r="N18" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="85">
+        <v>0.0014</v>
+      </c>
+      <c r="P18" s="60">
         <f t="shared" si="1"/>
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q18" s="29">
-        <v>1.4E-3</v>
-      </c>
-      <c r="R18" s="27">
+        <v>0.0028</v>
+      </c>
+      <c r="Q18" s="60">
+        <v>0.0014</v>
+      </c>
+      <c r="R18" s="109">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="50"/>
+        <v>0.14</v>
+      </c>
+      <c r="S18" s="17"/>
+      <c r="T18" s="110"/>
+      <c r="U18" s="112"/>
     </row>
-    <row r="19" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A19" s="2">
+    <row r="19" ht="15.75" spans="1:21">
+      <c r="A19" s="8">
         <v>17</v>
       </c>
-      <c r="B19" s="154"/>
-      <c r="C19" s="87" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="67" t="s">
-        <v>125</v>
-      </c>
-      <c r="G19" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="K19" s="7">
+      <c r="B19" s="15"/>
+      <c r="C19" s="173" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="146" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="146" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="148" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="146" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" s="17">
         <v>100</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="17">
         <v>3</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="23">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N19" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="40">
-        <v>1.4E-3</v>
-      </c>
-      <c r="P19" s="29">
+      <c r="N19" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" s="85">
+        <v>0.0014</v>
+      </c>
+      <c r="P19" s="60">
         <f t="shared" si="1"/>
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q19" s="29">
-        <v>1.4E-3</v>
-      </c>
-      <c r="R19" s="27">
+        <v>0.0042</v>
+      </c>
+      <c r="Q19" s="60">
+        <v>0.0014</v>
+      </c>
+      <c r="R19" s="109">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="50"/>
+        <v>0.14</v>
+      </c>
+      <c r="S19" s="17"/>
+      <c r="T19" s="110"/>
+      <c r="U19" s="112"/>
     </row>
-    <row r="20" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A20" s="2">
+    <row r="20" ht="15.75" spans="1:21">
+      <c r="A20" s="8">
         <v>18</v>
       </c>
-      <c r="B20" s="154"/>
-      <c r="C20" s="87" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="67" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="173" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J20" s="67" t="s">
+      <c r="D20" s="146" t="s">
         <v>134</v>
       </c>
-      <c r="K20" s="7">
+      <c r="E20" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="146" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I20" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="146" t="s">
+        <v>139</v>
+      </c>
+      <c r="K20" s="17">
         <v>20</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="17">
         <v>2</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N20" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="19">
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="P20" s="29">
+      <c r="N20" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="86">
+        <v>0.0295</v>
+      </c>
+      <c r="P20" s="60">
         <f t="shared" si="1"/>
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="Q20" s="29">
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="R20" s="27">
+        <v>0.059</v>
+      </c>
+      <c r="Q20" s="60">
+        <v>0.0295</v>
+      </c>
+      <c r="R20" s="109">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="50"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="110"/>
+      <c r="U20" s="112"/>
     </row>
-    <row r="21" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A21" s="2">
+    <row r="21" ht="15.75" spans="1:21">
+      <c r="A21" s="8">
         <v>19</v>
       </c>
-      <c r="B21" s="154"/>
-      <c r="C21" s="87" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="173" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="146" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="146" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" s="97" t="s">
-        <v>137</v>
-      </c>
-      <c r="G21" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="I21" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="J21" s="67" t="s">
-        <v>141</v>
-      </c>
-      <c r="K21" s="7">
+      <c r="F21" s="149" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="148" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="148" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="146" t="s">
+        <v>146</v>
+      </c>
+      <c r="K21" s="17">
         <v>10</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="17">
         <v>1</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N21" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="40">
+      <c r="N21" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="85">
         <v>0.1133</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="60">
         <f t="shared" si="1"/>
         <v>0.1133</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="60">
         <v>0.1133</v>
       </c>
-      <c r="R21" s="27">
+      <c r="R21" s="109">
         <f t="shared" si="2"/>
         <v>1.133</v>
       </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="50"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="110"/>
+      <c r="U21" s="112"/>
     </row>
-    <row r="22" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A22" s="2">
+    <row r="22" ht="15.75" spans="1:21">
+      <c r="A22" s="8">
         <v>20</v>
       </c>
-      <c r="B22" s="154"/>
-      <c r="C22" s="87" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="67" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="G22" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="I22" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J22" s="67" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="173" t="s">
         <v>147</v>
       </c>
-      <c r="K22" s="7">
+      <c r="D22" s="146" t="s">
+        <v>148</v>
+      </c>
+      <c r="E22" s="146" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="146" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="148" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="146" t="s">
+        <v>152</v>
+      </c>
+      <c r="K22" s="17">
         <v>100</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L22" s="17">
         <v>1</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N22" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" s="40">
-        <v>2.8E-3</v>
-      </c>
-      <c r="P22" s="29">
+      <c r="N22" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="85">
+        <v>0.0028</v>
+      </c>
+      <c r="P22" s="60">
         <f t="shared" si="1"/>
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q22" s="29">
-        <v>2.8E-3</v>
-      </c>
-      <c r="R22" s="27">
+        <v>0.0028</v>
+      </c>
+      <c r="Q22" s="60">
+        <v>0.0028</v>
+      </c>
+      <c r="R22" s="109">
         <f t="shared" si="2"/>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="50"/>
+        <v>0.28</v>
+      </c>
+      <c r="S22" s="17"/>
+      <c r="T22" s="110"/>
+      <c r="U22" s="112"/>
     </row>
-    <row r="23" spans="1:21" s="95" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A23" s="2">
+    <row r="23" s="1" customFormat="1" ht="15.75" spans="1:21">
+      <c r="A23" s="8">
         <v>21</v>
       </c>
-      <c r="B23" s="155"/>
-      <c r="C23" s="89" t="s">
-        <v>148</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="76" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="I23" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="J23" s="76" t="s">
-        <v>152</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="B23" s="26"/>
+      <c r="C23" s="175" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="156" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="156" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="159" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="156" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="156" t="s">
+        <v>157</v>
+      </c>
+      <c r="K23" s="28">
         <v>100</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="31">
         <v>8</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="29">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N23" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" s="38">
-        <v>1.8E-3</v>
-      </c>
-      <c r="P23" s="33">
+      <c r="N23" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" s="73">
+        <v>0.0018</v>
+      </c>
+      <c r="P23" s="68">
         <f t="shared" si="1"/>
-        <v>1.44E-2</v>
-      </c>
-      <c r="Q23" s="33">
-        <v>1.8E-3</v>
-      </c>
-      <c r="R23" s="34">
+        <v>0.0144</v>
+      </c>
+      <c r="Q23" s="68">
+        <v>0.0018</v>
+      </c>
+      <c r="R23" s="115">
         <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
-      <c r="S23" s="14"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="124"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="116"/>
+      <c r="U23" s="123"/>
     </row>
-    <row r="24" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A24" s="2">
+    <row r="24" ht="15.75" spans="1:21">
+      <c r="A24" s="8">
         <v>22</v>
       </c>
-      <c r="B24" s="153" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="129" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="130" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" s="130" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="130" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24" s="131" t="s">
+      <c r="B24" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="H24" s="131" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="130" t="s">
-        <v>61</v>
-      </c>
-      <c r="J24" s="131" t="s">
-        <v>93</v>
-      </c>
-      <c r="K24" s="132">
+      <c r="C24" s="176" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="177" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="177" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="177" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="178" t="s">
+        <v>163</v>
+      </c>
+      <c r="H24" s="178" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="177" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="K24" s="45">
         <v>10</v>
       </c>
-      <c r="L24" s="132">
+      <c r="L24" s="45">
         <v>1</v>
       </c>
-      <c r="M24" s="133">
+      <c r="M24" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="134" t="s">
-        <v>159</v>
-      </c>
-      <c r="O24" s="135">
+      <c r="N24" s="88" t="s">
+        <v>164</v>
+      </c>
+      <c r="O24" s="89">
         <v>1.2</v>
       </c>
-      <c r="P24" s="135">
+      <c r="P24" s="89">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="Q24" s="135">
+      <c r="Q24" s="89">
         <v>1.2</v>
       </c>
-      <c r="R24" s="136">
+      <c r="R24" s="124">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="S24" s="137" t="s">
-        <v>212</v>
-      </c>
-      <c r="T24" s="138">
-        <v>4.7619999999999996</v>
-      </c>
-      <c r="U24" s="50"/>
+      <c r="S24" s="125" t="s">
+        <v>165</v>
+      </c>
+      <c r="T24" s="126">
+        <v>4.762</v>
+      </c>
+      <c r="U24" s="112"/>
     </row>
-    <row r="25" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A25" s="2">
+    <row r="25" ht="15.75" spans="1:21">
+      <c r="A25" s="8">
         <v>23</v>
       </c>
-      <c r="B25" s="154"/>
-      <c r="C25" s="87" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="72" t="s">
-        <v>164</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="I25" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J25" s="72" t="s">
-        <v>93</v>
-      </c>
-      <c r="K25" s="12">
+      <c r="B25" s="15"/>
+      <c r="C25" s="173" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="146" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="146" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="146" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="148" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="148" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" s="25">
         <v>6</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="25">
         <v>1</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N25" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" s="40">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="P25" s="29">
+      <c r="N25" s="174" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="85">
+        <v>0.278</v>
+      </c>
+      <c r="P25" s="60">
         <f t="shared" si="1"/>
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="Q25" s="29">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="R25" s="27">
+        <v>0.278</v>
+      </c>
+      <c r="Q25" s="60">
+        <v>0.278</v>
+      </c>
+      <c r="R25" s="109">
         <f t="shared" si="2"/>
-        <v>1.6680000000000001</v>
-      </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="51"/>
-      <c r="U25" s="50"/>
+        <v>1.668</v>
+      </c>
+      <c r="S25" s="17"/>
+      <c r="T25" s="110"/>
+      <c r="U25" s="112"/>
     </row>
-    <row r="26" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A26" s="2">
+    <row r="26" ht="15.75" spans="1:21">
+      <c r="A26" s="8">
         <v>24</v>
       </c>
-      <c r="B26" s="155"/>
-      <c r="C26" s="89" t="s">
-        <v>166</v>
-      </c>
-      <c r="D26" s="76" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" s="76" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="76" t="s">
-        <v>169</v>
-      </c>
-      <c r="G26" s="78" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="J26" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="K26" s="16">
+      <c r="B26" s="26"/>
+      <c r="C26" s="175" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="156" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="156" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="156" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="159" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" s="156" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="159" t="s">
+        <v>178</v>
+      </c>
+      <c r="K26" s="31">
         <v>6</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="31">
         <v>1</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N26" s="116" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" s="38">
-        <v>0.16980000000000001</v>
-      </c>
-      <c r="P26" s="33">
+      <c r="N26" s="179" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="73">
+        <v>0.1698</v>
+      </c>
+      <c r="P26" s="68">
         <f t="shared" si="1"/>
-        <v>0.16980000000000001</v>
-      </c>
-      <c r="Q26" s="33">
-        <v>0.16980000000000001</v>
-      </c>
-      <c r="R26" s="34">
+        <v>0.1698</v>
+      </c>
+      <c r="Q26" s="68">
+        <v>0.1698</v>
+      </c>
+      <c r="R26" s="115">
         <f t="shared" si="2"/>
-        <v>1.0188000000000001</v>
-      </c>
-      <c r="S26" s="56"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="50"/>
+        <v>1.0188</v>
+      </c>
+      <c r="S26" s="117"/>
+      <c r="T26" s="116"/>
+      <c r="U26" s="112"/>
     </row>
-    <row r="27" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A27" s="2">
+    <row r="27" ht="15.75" spans="1:21">
+      <c r="A27" s="8">
         <v>25</v>
       </c>
-      <c r="B27" s="153" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="129" t="s">
-        <v>173</v>
-      </c>
-      <c r="D27" s="130" t="s">
-        <v>174</v>
-      </c>
-      <c r="E27" s="130" t="s">
-        <v>175</v>
-      </c>
-      <c r="F27" s="130" t="s">
-        <v>175</v>
-      </c>
-      <c r="G27" s="130" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="130" t="s">
-        <v>61</v>
-      </c>
-      <c r="I27" s="130" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="130" t="s">
-        <v>93</v>
-      </c>
-      <c r="K27" s="133">
+      <c r="B27" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="176" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="177" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="177" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="177" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="177" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" s="177" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="177" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="177" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" s="44">
         <v>100</v>
       </c>
-      <c r="L27" s="133">
+      <c r="L27" s="44">
         <v>1</v>
       </c>
-      <c r="M27" s="133">
+      <c r="M27" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N27" s="139" t="s">
-        <v>177</v>
-      </c>
-      <c r="O27" s="135">
+      <c r="N27" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="O27" s="89">
         <v>36.9</v>
       </c>
-      <c r="P27" s="135">
+      <c r="P27" s="89">
         <f t="shared" si="1"/>
         <v>36.9</v>
       </c>
-      <c r="Q27" s="135">
-        <v>0.36899999999999999</v>
-      </c>
-      <c r="R27" s="136">
+      <c r="Q27" s="89">
+        <v>0.369</v>
+      </c>
+      <c r="R27" s="124">
         <f t="shared" si="2"/>
         <v>36.9</v>
       </c>
-      <c r="S27" s="140" t="s">
-        <v>213</v>
-      </c>
-      <c r="T27" s="138"/>
-      <c r="U27" s="50"/>
+      <c r="S27" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="T27" s="126"/>
+      <c r="U27" s="112"/>
     </row>
-    <row r="28" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A28" s="2">
+    <row r="28" ht="15.75" spans="1:21">
+      <c r="A28" s="8">
         <v>26</v>
       </c>
-      <c r="B28" s="154"/>
-      <c r="C28" s="141" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="142" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="142" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="142" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="142" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="142" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="180" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="181" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="142" t="s">
-        <v>61</v>
-      </c>
-      <c r="J28" s="143" t="s">
-        <v>215</v>
-      </c>
-      <c r="K28" s="144">
+      <c r="F28" s="181" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="181" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="181" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="181" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="182" t="s">
+        <v>190</v>
+      </c>
+      <c r="K28" s="92">
         <v>12</v>
       </c>
-      <c r="L28" s="145">
+      <c r="L28" s="47">
         <v>2</v>
       </c>
-      <c r="M28" s="145">
+      <c r="M28" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28" s="146" t="s">
-        <v>182</v>
-      </c>
-      <c r="O28" s="147">
+      <c r="N28" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="O28" s="94">
         <v>0.75</v>
       </c>
-      <c r="P28" s="148">
+      <c r="P28" s="95">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="Q28" s="147">
+      <c r="Q28" s="94">
         <v>0.75</v>
       </c>
-      <c r="R28" s="149">
+      <c r="R28" s="96">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="S28" s="150"/>
-      <c r="T28" s="151"/>
-      <c r="U28" s="50"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="129"/>
+      <c r="U28" s="112"/>
     </row>
-    <row r="29" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A29" s="2">
+    <row r="29" ht="15.75" spans="1:21">
+      <c r="A29" s="8">
         <v>27</v>
       </c>
-      <c r="B29" s="154"/>
-      <c r="C29" s="141" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="180" t="s">
+        <v>192</v>
+      </c>
+      <c r="D29" s="181" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" s="181" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="181" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" s="181" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="142" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="142" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="142" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="142" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="142" t="s">
-        <v>61</v>
-      </c>
-      <c r="J29" s="143" t="s">
-        <v>93</v>
-      </c>
-      <c r="K29" s="144">
+      <c r="H29" s="181" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="181" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="182" t="s">
+        <v>97</v>
+      </c>
+      <c r="K29" s="92">
         <v>10</v>
       </c>
-      <c r="L29" s="145">
+      <c r="L29" s="47">
         <v>1</v>
       </c>
-      <c r="M29" s="145">
+      <c r="M29" s="47">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N29" s="146" t="s">
-        <v>177</v>
-      </c>
-      <c r="O29" s="152">
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="P29" s="148">
+      <c r="N29" s="93" t="s">
+        <v>184</v>
+      </c>
+      <c r="O29" s="96">
+        <v>0.553</v>
+      </c>
+      <c r="P29" s="95">
         <f t="shared" si="1"/>
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="Q29" s="148">
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="R29" s="149">
+        <v>0.553</v>
+      </c>
+      <c r="Q29" s="95">
+        <v>0.553</v>
+      </c>
+      <c r="R29" s="96">
         <f t="shared" si="2"/>
         <v>5.53</v>
       </c>
-      <c r="S29" s="150"/>
-      <c r="T29" s="151"/>
-      <c r="U29" s="50"/>
+      <c r="S29" s="128"/>
+      <c r="T29" s="129"/>
+      <c r="U29" s="112"/>
     </row>
-    <row r="30" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A30" s="2">
+    <row r="30" ht="15.75" spans="1:21">
+      <c r="A30" s="8">
         <v>28</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="87" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="E30" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="G30" s="67" t="s">
+      <c r="B30" s="15"/>
+      <c r="C30" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="146" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="146" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="146" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="146" t="s">
+        <v>197</v>
+      </c>
+      <c r="I30" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="148" t="s">
         <v>190</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="I30" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J30" s="72" t="s">
-        <v>215</v>
-      </c>
-      <c r="K30" s="12">
+      <c r="K30" s="25">
         <v>20</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="17">
         <v>1</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="19">
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="P30" s="29">
-        <f t="shared" si="1"/>
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="Q30" s="29">
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="R30" s="27">
-        <f t="shared" si="2"/>
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="S30" s="53"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="50"/>
+      <c r="N30" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="98">
+        <v>0.0263</v>
+      </c>
+      <c r="P30" s="99">
+        <f>O30*L30</f>
+        <v>0.0263</v>
+      </c>
+      <c r="Q30" s="130">
+        <v>0.0263</v>
+      </c>
+      <c r="R30" s="131">
+        <f>Q30*K30</f>
+        <v>0.526</v>
+      </c>
+      <c r="S30" s="113"/>
+      <c r="T30" s="110"/>
+      <c r="U30" s="112"/>
     </row>
-    <row r="31" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A31" s="2">
+    <row r="31" ht="15.75" spans="1:21">
+      <c r="A31" s="8">
         <v>29</v>
       </c>
-      <c r="B31" s="154"/>
-      <c r="C31" s="87" t="s">
-        <v>192</v>
-      </c>
-      <c r="D31" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="F31" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="G31" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I31" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J31" s="72" t="s">
-        <v>93</v>
-      </c>
-      <c r="K31" s="12">
+      <c r="B31" s="15"/>
+      <c r="C31" s="173" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="F31" s="146" t="s">
+        <v>202</v>
+      </c>
+      <c r="G31" s="146" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="I31" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="148" t="s">
+        <v>97</v>
+      </c>
+      <c r="K31" s="25">
         <v>15</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="25">
         <v>2</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N31" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="40">
+      <c r="N31" s="183" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="85">
         <v>0.1085</v>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="60">
         <f t="shared" si="1"/>
         <v>0.217</v>
       </c>
-      <c r="Q31" s="29">
+      <c r="Q31" s="60">
         <v>0.1085</v>
       </c>
-      <c r="R31" s="27">
+      <c r="R31" s="109">
         <f t="shared" si="2"/>
-        <v>1.6274999999999999</v>
-      </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="50"/>
+        <v>1.6275</v>
+      </c>
+      <c r="S31" s="17"/>
+      <c r="T31" s="110"/>
+      <c r="U31" s="112"/>
     </row>
-    <row r="32" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A32" s="2">
+    <row r="32" ht="15.75" spans="1:21">
+      <c r="A32" s="8">
         <v>30</v>
       </c>
-      <c r="B32" s="154"/>
-      <c r="C32" s="91" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20">
+      <c r="B32" s="15"/>
+      <c r="C32" s="184" t="s">
+        <v>205</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="185" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49">
         <v>5</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M32" s="23">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N32" s="20"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="T32" s="58"/>
-      <c r="U32" s="50"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="101"/>
+      <c r="R32" s="132"/>
+      <c r="S32" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="T32" s="134"/>
+      <c r="U32" s="112"/>
     </row>
-    <row r="33" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A33" s="102">
+    <row r="33" ht="15.75" spans="1:21">
+      <c r="A33" s="50">
         <v>31</v>
       </c>
-      <c r="B33" s="155"/>
-      <c r="C33" s="93" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E33" s="94" t="s">
-        <v>204</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21">
+      <c r="B33" s="26"/>
+      <c r="C33" s="186" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" s="187" t="s">
+        <v>211</v>
+      </c>
+      <c r="F33" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52">
         <v>5</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33" s="29">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N33" s="21"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="T33" s="60"/>
-      <c r="U33" s="50"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="102"/>
+      <c r="P33" s="102"/>
+      <c r="Q33" s="102"/>
+      <c r="R33" s="135"/>
+      <c r="S33" s="136" t="s">
+        <v>208</v>
+      </c>
+      <c r="T33" s="137"/>
+      <c r="U33" s="112"/>
     </row>
-    <row r="34" spans="1:21" ht="16.5" thickBot="1">
+    <row r="34" ht="16.5" spans="1:21">
       <c r="A34"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="156" t="s">
-        <v>205</v>
-      </c>
-      <c r="M34" s="156"/>
-      <c r="N34" s="156"/>
-      <c r="P34" s="125">
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="103" t="s">
+        <v>212</v>
+      </c>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="P34" s="104">
         <f>SUM(P3:P31)</f>
-        <v>43.337799999999994</v>
-      </c>
-      <c r="R34" s="47">
+        <v>43.3427</v>
+      </c>
+      <c r="R34" s="138">
         <f>SUM(R3:R31)</f>
-        <v>89.254799999999989</v>
-      </c>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="50"/>
+        <v>89.3528</v>
+      </c>
+      <c r="S34" s="53"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="112"/>
     </row>
-    <row r="35" spans="1:21" ht="16.5" thickBot="1">
+    <row r="35" ht="16.5" spans="1:21">
       <c r="A35"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="157" t="s">
-        <v>206</v>
-      </c>
-      <c r="M35" s="157"/>
-      <c r="N35" s="157"/>
-      <c r="R35" s="48">
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="105" t="s">
+        <v>213</v>
+      </c>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="R35" s="139">
         <f>R34/5</f>
-        <v>17.850959999999997</v>
-      </c>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="50"/>
+        <v>17.87056</v>
+      </c>
+      <c r="S35" s="53"/>
+      <c r="T35" s="53"/>
+      <c r="U35" s="112"/>
     </row>
     <row r="36" spans="1:21">
       <c r="A36"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
+      <c r="T36" s="112"/>
+      <c r="U36" s="112"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
+      <c r="T37" s="112"/>
+      <c r="U37" s="112"/>
     </row>
     <row r="38" spans="1:21">
       <c r="A38"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
+      <c r="T38" s="112"/>
+      <c r="U38" s="112"/>
     </row>
     <row r="39" spans="1:21">
       <c r="A39"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
+      <c r="T39" s="112"/>
+      <c r="U39" s="112"/>
     </row>
     <row r="40" spans="1:21">
       <c r="A40"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="50"/>
+      <c r="T40" s="112"/>
+      <c r="U40" s="112"/>
     </row>
     <row r="41" spans="1:21">
       <c r="A41"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="50"/>
+      <c r="T41" s="112"/>
+      <c r="U41" s="112"/>
     </row>
     <row r="42" spans="1:21">
       <c r="A42"/>
-      <c r="T42" s="50"/>
-      <c r="U42" s="50"/>
+      <c r="T42" s="112"/>
+      <c r="U42" s="112"/>
     </row>
-    <row r="43" spans="1:21" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="1:21">
       <c r="A43"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
+      <c r="T43" s="112"/>
+      <c r="U43" s="112"/>
     </row>
     <row r="44" spans="1:21">
       <c r="A44"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
+      <c r="T44" s="112"/>
+      <c r="U44" s="112"/>
     </row>
     <row r="45" spans="1:21">
       <c r="A45"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
+      <c r="T45" s="112"/>
+      <c r="U45" s="112"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46"/>
-      <c r="T46" s="50"/>
-      <c r="U46" s="50"/>
+      <c r="T46" s="112"/>
+      <c r="U46" s="112"/>
     </row>
     <row r="47" spans="1:21">
       <c r="A47"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
+      <c r="T47" s="112"/>
+      <c r="U47" s="112"/>
     </row>
     <row r="48" spans="1:21">
       <c r="A48"/>
-      <c r="T48" s="50"/>
-      <c r="U48" s="50"/>
+      <c r="T48" s="112"/>
+      <c r="U48" s="112"/>
     </row>
     <row r="49" spans="8:19">
-      <c r="H49" s="23"/>
-      <c r="S49" s="61"/>
+      <c r="H49" s="54"/>
+      <c r="S49" s="140"/>
     </row>
     <row r="50" spans="8:19">
-      <c r="H50" s="23"/>
-      <c r="S50" s="61"/>
+      <c r="H50" s="54"/>
+      <c r="S50" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B27:B33"/>
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L35:N35"/>
-    <mergeCell ref="A1:T1"/>
     <mergeCell ref="B3:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B17:B23"/>
     <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B33"/>
   </mergeCells>
   <conditionalFormatting sqref="S11">
     <cfRule type="dataBar" priority="41">
@@ -4105,7 +4804,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C74B87F2-CE14-491B-84E1-06E8048F6B06}</x14:id>
+          <x14:id>{91b8d679-ff0b-4b19-a610-6c243faf4003}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4119,7 +4818,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7CA57324-CAEC-4B95-AFA1-571FAD1F065E}</x14:id>
+          <x14:id>{8602b36a-2b77-4657-823a-0d7b51a8c0d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4133,7 +4832,21 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9727F6DD-832B-4E53-B952-BA82A5D4789A}</x14:id>
+          <x14:id>{f78c7e8a-5679-42c3-8c50-13119118a4a2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S24">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFD6007B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4c28e1de-fd45-4e1a-bdb3-0d57d1810c06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4181,7 +4894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8F0627EC-9E46-490D-8337-4AFCD6A94ACA}</x14:id>
+          <x14:id>{ea91e7cb-e035-4d5f-bd6b-48dfb63ccbdb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4217,7 +4930,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F9379B80-DD0E-4C4F-BD4F-B563C9CC9DF4}</x14:id>
+          <x14:id>{72f02937-73f0-4b31-b5ca-2d756df15d65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4231,7 +4944,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54C13508-4B69-4979-B79B-BF833A04A08F}</x14:id>
+          <x14:id>{54c4f5f8-ede7-4601-aeac-8e612bf30c27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4257,7 +4970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B79DB715-26B6-477C-A2BD-B4E05B3329D5}</x14:id>
+          <x14:id>{94e20060-874b-439f-8fda-33b3dd39ffe6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4271,7 +4984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2E387700-2475-4F55-AB7B-24274A2284A5}</x14:id>
+          <x14:id>{dbb933a5-5d45-42ae-8d8b-f05439ef033d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4285,7 +4998,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D68A17A8-314A-4563-8813-D56E443F2953}</x14:id>
+          <x14:id>{ffb8fd96-bb87-47dd-9e3b-fba7e127703c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4299,7 +5012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FA569F89-D7CA-46CF-933E-D8C90500C260}</x14:id>
+          <x14:id>{dc4f43e8-ca2d-4f5a-a416-ccdf4c097d17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4328,56 +5041,43 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S24">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFD6007B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7F28AD41-B31C-490A-8305-C9BDA5E3CED3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N8" r:id="rId1"/>
-    <hyperlink ref="N9" r:id="rId2"/>
-    <hyperlink ref="N10" r:id="rId3"/>
-    <hyperlink ref="N11" r:id="rId4"/>
-    <hyperlink ref="N12" r:id="rId5"/>
-    <hyperlink ref="N13" r:id="rId6"/>
-    <hyperlink ref="N14" r:id="rId7"/>
-    <hyperlink ref="N17" r:id="rId8"/>
-    <hyperlink ref="N18" r:id="rId9"/>
-    <hyperlink ref="N19" r:id="rId10"/>
-    <hyperlink ref="N20" r:id="rId11"/>
-    <hyperlink ref="N22" r:id="rId12"/>
-    <hyperlink ref="N23" r:id="rId13"/>
-    <hyperlink ref="N25" r:id="rId14"/>
-    <hyperlink ref="N26" r:id="rId15"/>
-    <hyperlink ref="N31" r:id="rId16"/>
-    <hyperlink ref="N6" r:id="rId17"/>
-    <hyperlink ref="N7" r:id="rId18"/>
-    <hyperlink ref="N21" r:id="rId19"/>
-    <hyperlink ref="N24" r:id="rId20"/>
-    <hyperlink ref="N3" r:id="rId21"/>
-    <hyperlink ref="N4" r:id="rId22"/>
-    <hyperlink ref="N5" r:id="rId23"/>
-    <hyperlink ref="N27" r:id="rId24"/>
-    <hyperlink ref="N29" r:id="rId25"/>
-    <hyperlink ref="N30" r:id="rId26"/>
-    <hyperlink ref="N15" r:id="rId27"/>
+    <hyperlink ref="N8" r:id="rId1" display="LCSC"/>
+    <hyperlink ref="N9" r:id="rId2" display="LCSC"/>
+    <hyperlink ref="N10" r:id="rId3" display="LCSC"/>
+    <hyperlink ref="N11" r:id="rId4" display="LCSC"/>
+    <hyperlink ref="N12" r:id="rId5" display="LCSC"/>
+    <hyperlink ref="N13" r:id="rId6" display="LCSC"/>
+    <hyperlink ref="N14" r:id="rId7" display="LCSC"/>
+    <hyperlink ref="N17" r:id="rId8" display="LCSC"/>
+    <hyperlink ref="N18" r:id="rId9" display="LCSC"/>
+    <hyperlink ref="N19" r:id="rId10" display="LCSC"/>
+    <hyperlink ref="N20" r:id="rId11" display="LCSC"/>
+    <hyperlink ref="N22" r:id="rId12" display="LCSC"/>
+    <hyperlink ref="N23" r:id="rId13" display="LCSC"/>
+    <hyperlink ref="N25" r:id="rId14" display="LCSC"/>
+    <hyperlink ref="N26" r:id="rId15" display="LCSC"/>
+    <hyperlink ref="N31" r:id="rId16" display="LCSC"/>
+    <hyperlink ref="N6" r:id="rId17" display="LCSC"/>
+    <hyperlink ref="N7" r:id="rId18" display="LCSC"/>
+    <hyperlink ref="N21" r:id="rId19" display="LCSC"/>
+    <hyperlink ref="N24" r:id="rId20" display="Alibaba"/>
+    <hyperlink ref="N3" r:id="rId21" display="LCSC"/>
+    <hyperlink ref="N4" r:id="rId22" display="LCSC"/>
+    <hyperlink ref="N5" r:id="rId23" display="LCSC"/>
+    <hyperlink ref="N27" r:id="rId24" display="Aliexpress"/>
+    <hyperlink ref="N29" r:id="rId25" display="Aliexpress"/>
+    <hyperlink ref="N15" r:id="rId26" display="LCSC"/>
+    <hyperlink ref="N30" r:id="rId27" display="LCSC"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId28"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C74B87F2-CE14-491B-84E1-06E8048F6B06}">
+          <x14:cfRule type="dataBar" id="{91b8d679-ff0b-4b19-a610-6c243faf4003}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4390,7 +5090,7 @@
           <xm:sqref>S11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7CA57324-CAEC-4B95-AFA1-571FAD1F065E}">
+          <x14:cfRule type="dataBar" id="{8602b36a-2b77-4657-823a-0d7b51a8c0d4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4403,7 +5103,7 @@
           <xm:sqref>S15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9727F6DD-832B-4E53-B952-BA82A5D4789A}">
+          <x14:cfRule type="dataBar" id="{f78c7e8a-5679-42c3-8c50-13119118a4a2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4416,7 +5116,20 @@
           <xm:sqref>N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8F0627EC-9E46-490D-8337-4AFCD6A94ACA}">
+          <x14:cfRule type="dataBar" id="{4c28e1de-fd45-4e1a-bdb3-0d57d1810c06}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ea91e7cb-e035-4d5f-bd6b-48dfb63ccbdb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4429,7 +5142,7 @@
           <xm:sqref>S32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F9379B80-DD0E-4C4F-BD4F-B563C9CC9DF4}">
+          <x14:cfRule type="dataBar" id="{72f02937-73f0-4b31-b5ca-2d756df15d65}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4442,7 +5155,7 @@
           <xm:sqref>S33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{54C13508-4B69-4979-B79B-BF833A04A08F}">
+          <x14:cfRule type="dataBar" id="{54c4f5f8-ede7-4601-aeac-8e612bf30c27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4455,7 +5168,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B79DB715-26B6-477C-A2BD-B4E05B3329D5}">
+          <x14:cfRule type="dataBar" id="{94e20060-874b-439f-8fda-33b3dd39ffe6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4468,7 +5181,7 @@
           <xm:sqref>N3:N4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2E387700-2475-4F55-AB7B-24274A2284A5}">
+          <x14:cfRule type="dataBar" id="{dbb933a5-5d45-42ae-8d8b-f05439ef033d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4481,7 +5194,7 @@
           <xm:sqref>N23:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D68A17A8-314A-4563-8813-D56E443F2953}">
+          <x14:cfRule type="dataBar" id="{ffb8fd96-bb87-47dd-9e3b-fba7e127703c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4494,7 +5207,7 @@
           <xm:sqref>R3:R33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FA569F89-D7CA-46CF-933E-D8C90500C260}">
+          <x14:cfRule type="dataBar" id="{dc4f43e8-ca2d-4f5a-a416-ccdf4c097d17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4506,19 +5219,6 @@
           </x14:cfRule>
           <xm:sqref>S27:S30</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7F28AD41-B31C-490A-8305-C9BDA5E3CED3}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFD6007B"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>S24</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/LCSC_Interface_Board.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XPENDER\Documents\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9795"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -229,13 +234,7 @@
     <t>C487384</t>
   </si>
   <si>
-    <t>CAP ALUM 10uF 25V SMD</t>
-  </si>
-  <si>
     <t>C1</t>
-  </si>
-  <si>
-    <t>RVT1E100M0405</t>
   </si>
   <si>
     <t>Honor Elec</t>
@@ -587,7 +586,7 @@
     <t>MOQ=100</t>
   </si>
   <si>
-    <t>10/100 BASE-TX RJ45 WITH LEDS
+    <t>10/100 BASE-TX RJ45 WITH LEDS_x000D_
 INTEGRATED MAGNETICS CONNECTOR</t>
   </si>
   <si>
@@ -670,22 +669,24 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73J</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,144 +864,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1033,7 +898,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1043,194 +908,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="36">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1581,262 +1260,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1852,9 +1286,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1870,572 +1301,475 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="11" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="6" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="6" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="22" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="19" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="23" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="22" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2693,119 +2027,119 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.14285714285714" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="62.1809523809524" customWidth="1"/>
-    <col min="4" max="4" width="34.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="62.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="26.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="15.2857142857143" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="11.5714285714286" customWidth="1"/>
-    <col min="12" max="12" width="21.8571428571429" customWidth="1"/>
-    <col min="13" max="13" width="14.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="16.2857142857143" customWidth="1"/>
-    <col min="15" max="15" width="12.7142857142857" customWidth="1"/>
-    <col min="16" max="17" width="14.2857142857143" customWidth="1"/>
-    <col min="18" max="18" width="13.4285714285714" customWidth="1"/>
-    <col min="19" max="19" width="14.1428571428571" customWidth="1"/>
-    <col min="20" max="20" width="50.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" customWidth="1"/>
+    <col min="20" max="20" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:20">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:36" ht="15.75">
+      <c r="A1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="106"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:36">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="158"/>
+      <c r="S1" s="158"/>
+      <c r="T1" s="159"/>
+    </row>
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="15.75">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="56" t="s">
+      <c r="P2" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="56" t="s">
+      <c r="Q2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="U2"/>
@@ -2825,1964 +2159,1964 @@
       <c r="AI2"/>
       <c r="AJ2"/>
     </row>
-    <row r="3" ht="15.75" spans="1:20">
-      <c r="A3" s="8">
+    <row r="3" spans="1:36">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="141" t="s">
+      <c r="C3" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="142" t="s">
+      <c r="E3" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="143" t="s">
+      <c r="F3" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="142" t="s">
+      <c r="G3" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="144" t="s">
+      <c r="I3" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="142" t="s">
+      <c r="J3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="24">
         <v>50</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="9">
         <v>4</v>
       </c>
-      <c r="M3" s="33">
+      <c r="M3" s="24">
         <f>L3*5</f>
         <v>20</v>
       </c>
-      <c r="N3" s="57" t="s">
+      <c r="N3" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="58">
-        <v>0.0082</v>
-      </c>
-      <c r="P3" s="58">
+      <c r="O3" s="40">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="P3" s="40">
         <f>O3*L3</f>
-        <v>0.0328</v>
-      </c>
-      <c r="Q3" s="58">
-        <v>0.0082</v>
-      </c>
-      <c r="R3" s="107">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="Q3" s="40">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="R3" s="76">
         <f>Q3*K3</f>
-        <v>0.41</v>
-      </c>
-      <c r="S3" s="33"/>
-      <c r="T3" s="108"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:20">
-      <c r="A4" s="8">
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="S3" s="24"/>
+      <c r="T3" s="77"/>
+    </row>
+    <row r="4" spans="1:36">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="145" t="s">
+      <c r="B4" s="163"/>
+      <c r="C4" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="146" t="s">
+      <c r="D4" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="147" t="s">
+      <c r="E4" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="146" t="s">
+      <c r="F4" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="147" t="s">
+      <c r="G4" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="148" t="s">
+      <c r="I4" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="147" t="s">
+      <c r="J4" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="17">
         <v>10</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="14">
         <v>1</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="17">
         <f t="shared" ref="M4:M33" si="0">L4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="59" t="s">
+      <c r="N4" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="60">
-        <v>0.0682</v>
-      </c>
-      <c r="P4" s="60">
+      <c r="O4" s="42">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="P4" s="42">
         <f t="shared" ref="P4:P31" si="1">O4*L4</f>
-        <v>0.0682</v>
-      </c>
-      <c r="Q4" s="60">
-        <v>0.0682</v>
-      </c>
-      <c r="R4" s="109">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="Q4" s="42">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="R4" s="78">
         <f t="shared" ref="R4:R31" si="2">Q4*K4</f>
-        <v>0.682</v>
-      </c>
-      <c r="S4" s="23"/>
-      <c r="T4" s="110"/>
-    </row>
-    <row r="5" ht="15.75" spans="1:20">
-      <c r="A5" s="8">
+        <v>0.68199999999999994</v>
+      </c>
+      <c r="S4" s="17"/>
+      <c r="T4" s="79"/>
+    </row>
+    <row r="5" spans="1:36">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="145" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="149" t="s">
+      <c r="F5" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="147" t="s">
+      <c r="G5" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="147" t="s">
+      <c r="J5" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="17">
         <v>100</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="14">
         <v>8</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="17">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N5" s="61" t="s">
+      <c r="N5" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="O5" s="60">
-        <v>0.0031</v>
-      </c>
-      <c r="P5" s="60">
+      <c r="O5" s="42">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="P5" s="42">
         <f t="shared" si="1"/>
-        <v>0.0248</v>
-      </c>
-      <c r="Q5" s="60">
-        <v>0.0031</v>
-      </c>
-      <c r="R5" s="109">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="Q5" s="42">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="R5" s="78">
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
-      <c r="S5" s="23"/>
-      <c r="T5" s="110"/>
-    </row>
-    <row r="6" ht="15.75" spans="1:20">
-      <c r="A6" s="8">
+      <c r="S5" s="17"/>
+      <c r="T5" s="79"/>
+    </row>
+    <row r="6" spans="1:36">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="150" t="s">
+      <c r="B6" s="163"/>
+      <c r="C6" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="151" t="s">
+      <c r="E6" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="149" t="s">
+      <c r="F6" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="152" t="s">
+      <c r="G6" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="146" t="s">
+      <c r="I6" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="151" t="s">
+      <c r="J6" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="17">
         <v>50</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="18">
         <v>3</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N6" s="153" t="s">
+      <c r="N6" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O6" s="60">
-        <v>0.0053</v>
-      </c>
-      <c r="P6" s="60">
+      <c r="O6" s="42">
+        <v>5.3E-3</v>
+      </c>
+      <c r="P6" s="42">
         <f t="shared" si="1"/>
-        <v>0.0159</v>
-      </c>
-      <c r="Q6" s="60">
-        <v>0.0053</v>
-      </c>
-      <c r="R6" s="109">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="Q6" s="42">
+        <v>5.3E-3</v>
+      </c>
+      <c r="R6" s="78">
         <f t="shared" si="2"/>
-        <v>0.265</v>
-      </c>
-      <c r="S6" s="23"/>
-      <c r="T6" s="110"/>
-    </row>
-    <row r="7" ht="15.75" spans="1:20">
-      <c r="A7" s="8">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="79"/>
+    </row>
+    <row r="7" spans="1:36">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="150" t="s">
+      <c r="B7" s="163"/>
+      <c r="C7" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="146" t="s">
+      <c r="D7" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="151" t="s">
+      <c r="E7" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="149" t="s">
+      <c r="F7" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="151" t="s">
+      <c r="J7" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="17">
         <v>10</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="18">
         <v>1</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N7" s="153" t="s">
+      <c r="N7" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="63">
-        <v>0.0403</v>
-      </c>
-      <c r="P7" s="60">
+      <c r="O7" s="44">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="P7" s="42">
         <f t="shared" si="1"/>
-        <v>0.0403</v>
-      </c>
-      <c r="Q7" s="60">
-        <v>0.0403</v>
-      </c>
-      <c r="R7" s="109">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="Q7" s="42">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="R7" s="78">
         <f t="shared" si="2"/>
-        <v>0.403</v>
-      </c>
-      <c r="S7" s="23"/>
-      <c r="T7" s="110"/>
-    </row>
-    <row r="8" ht="15.75" spans="1:20">
-      <c r="A8" s="8">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="S7" s="17"/>
+      <c r="T7" s="79"/>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="150" t="s">
+      <c r="B8" s="163"/>
+      <c r="C8" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="146" t="s">
+      <c r="D8" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="151" t="s">
+      <c r="E8" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="146" t="s">
+      <c r="F8" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="152" t="s">
+      <c r="G8" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="148" t="s">
+      <c r="I8" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="151" t="s">
+      <c r="J8" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="17">
         <v>10</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="45">
         <v>1</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="154" t="s">
+      <c r="N8" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="66">
-        <v>0.0759</v>
-      </c>
-      <c r="P8" s="60">
+      <c r="O8" s="46">
+        <v>7.5899999999999995E-2</v>
+      </c>
+      <c r="P8" s="42">
         <f t="shared" si="1"/>
-        <v>0.0759</v>
-      </c>
-      <c r="Q8" s="60">
-        <v>0.0759</v>
-      </c>
-      <c r="R8" s="109">
+        <v>7.5899999999999995E-2</v>
+      </c>
+      <c r="Q8" s="42">
+        <v>7.5899999999999995E-2</v>
+      </c>
+      <c r="R8" s="78">
         <f t="shared" si="2"/>
-        <v>0.759</v>
-      </c>
-      <c r="S8" s="111"/>
-      <c r="T8" s="110"/>
-    </row>
-    <row r="9" ht="15.75" spans="1:21">
-      <c r="A9" s="8">
+        <v>0.7589999999999999</v>
+      </c>
+      <c r="S8" s="80"/>
+      <c r="T8" s="79"/>
+    </row>
+    <row r="9" spans="1:36">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="150" t="s">
+      <c r="B9" s="163"/>
+      <c r="C9" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="146" t="s">
+      <c r="D9" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="151" t="s">
+      <c r="E9" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="146" t="s">
+      <c r="F9" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="152" t="s">
+      <c r="G9" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="148" t="s">
+      <c r="I9" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="151" t="s">
+      <c r="J9" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="17">
         <v>12</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="45">
         <v>2</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N9" s="154" t="s">
+      <c r="N9" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="66">
-        <v>0.1811</v>
-      </c>
-      <c r="P9" s="60">
+      <c r="O9" s="46">
+        <v>0.18110000000000001</v>
+      </c>
+      <c r="P9" s="42">
         <f t="shared" si="1"/>
-        <v>0.3622</v>
-      </c>
-      <c r="Q9" s="60">
-        <v>0.1811</v>
-      </c>
-      <c r="R9" s="109">
+        <v>0.36220000000000002</v>
+      </c>
+      <c r="Q9" s="42">
+        <v>0.18110000000000001</v>
+      </c>
+      <c r="R9" s="78">
         <f t="shared" si="2"/>
         <v>2.1732</v>
       </c>
-      <c r="S9" s="111"/>
-      <c r="T9" s="110"/>
-      <c r="U9" s="112"/>
-    </row>
-    <row r="10" ht="15.75" spans="1:21">
-      <c r="A10" s="8">
+      <c r="S9" s="80"/>
+      <c r="T9" s="79"/>
+      <c r="U9" s="81"/>
+    </row>
+    <row r="10" spans="1:36">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="150" t="s">
+      <c r="B10" s="163"/>
+      <c r="C10" s="165" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="146" t="s">
+      <c r="E10" s="120" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="166" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="151" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="146" t="s">
+      <c r="H10" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="152" t="s">
+      <c r="I10" s="117" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="148" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="151" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="23">
+      <c r="K10" s="17">
         <v>20</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="18">
         <v>1</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N10" s="153" t="s">
+      <c r="N10" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O10" s="60">
-        <v>0.0352</v>
-      </c>
-      <c r="P10" s="60">
+      <c r="O10" s="42">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="P10" s="42">
         <f t="shared" si="1"/>
-        <v>0.0352</v>
-      </c>
-      <c r="Q10" s="60">
-        <v>0.0352</v>
-      </c>
-      <c r="R10" s="109">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="Q10" s="42">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="R10" s="78">
         <f t="shared" si="2"/>
-        <v>0.704</v>
-      </c>
-      <c r="S10" s="23"/>
-      <c r="T10" s="110"/>
-      <c r="U10" s="112"/>
-    </row>
-    <row r="11" ht="15.75" spans="1:21">
-      <c r="A11" s="8">
+        <v>0.70400000000000007</v>
+      </c>
+      <c r="S10" s="17"/>
+      <c r="T10" s="79"/>
+      <c r="U10" s="81"/>
+    </row>
+    <row r="11" spans="1:36">
+      <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="150" t="s">
+      <c r="B11" s="163"/>
+      <c r="C11" s="119" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="115" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="146" t="s">
+      <c r="F11" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="151" t="s">
+      <c r="G11" s="121" t="s">
         <v>78</v>
       </c>
-      <c r="F11" s="146" t="s">
+      <c r="H11" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="152" t="s">
+      <c r="I11" s="117" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="148" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="151" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" s="23">
+      <c r="K11" s="17">
         <v>10</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="18">
         <v>1</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N11" s="153" t="s">
+      <c r="N11" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="60">
-        <v>0.0958</v>
-      </c>
-      <c r="P11" s="60">
+      <c r="O11" s="42">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="P11" s="42">
         <f t="shared" si="1"/>
-        <v>0.0958</v>
-      </c>
-      <c r="Q11" s="60">
-        <v>0.0958</v>
-      </c>
-      <c r="R11" s="109">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="Q11" s="42">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="R11" s="78">
         <f t="shared" si="2"/>
-        <v>0.958</v>
-      </c>
-      <c r="S11" s="113"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="114"/>
-    </row>
-    <row r="12" ht="15.75" spans="1:21">
-      <c r="A12" s="8">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="S11" s="82"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="83"/>
+    </row>
+    <row r="12" spans="1:36">
+      <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="155" t="s">
+      <c r="B12" s="164"/>
+      <c r="C12" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="125" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="156" t="s">
+      <c r="F12" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="157" t="s">
+      <c r="G12" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="156" t="s">
+      <c r="H12" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="158" t="s">
+      <c r="I12" s="128" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="126" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" s="159" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="157" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="29">
+      <c r="K12" s="21">
         <v>50</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="22">
         <v>1</v>
       </c>
-      <c r="M12" s="29">
+      <c r="M12" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="160" t="s">
+      <c r="N12" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="68">
-        <v>0.0147</v>
-      </c>
-      <c r="P12" s="68">
+      <c r="O12" s="47">
+        <v>1.47E-2</v>
+      </c>
+      <c r="P12" s="47">
         <f t="shared" si="1"/>
-        <v>0.0147</v>
-      </c>
-      <c r="Q12" s="68">
-        <v>0.0147</v>
-      </c>
-      <c r="R12" s="115">
+        <v>1.47E-2</v>
+      </c>
+      <c r="Q12" s="47">
+        <v>1.47E-2</v>
+      </c>
+      <c r="R12" s="84">
         <f t="shared" si="2"/>
-        <v>0.735</v>
-      </c>
-      <c r="S12" s="29"/>
-      <c r="T12" s="116"/>
-      <c r="U12" s="112"/>
-    </row>
-    <row r="13" ht="15.75" spans="1:21">
-      <c r="A13" s="8">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="S12" s="21"/>
+      <c r="T12" s="85"/>
+      <c r="U12" s="81"/>
+    </row>
+    <row r="13" spans="1:36">
+      <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="162" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="161" t="s">
+      <c r="E13" s="131" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="F13" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="162" t="s">
+      <c r="G13" s="131" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="143" t="s">
+      <c r="H13" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="162" t="s">
+      <c r="I13" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="132" t="s">
         <v>95</v>
       </c>
-      <c r="H13" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="163" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" s="33">
+      <c r="K13" s="24">
         <v>7</v>
       </c>
-      <c r="L13" s="70">
+      <c r="L13" s="48">
         <v>1</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N13" s="164" t="s">
+      <c r="N13" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="O13" s="58">
-        <v>0.3172</v>
-      </c>
-      <c r="P13" s="58">
+      <c r="O13" s="40">
+        <v>0.31719999999999998</v>
+      </c>
+      <c r="P13" s="40">
         <f t="shared" si="1"/>
-        <v>0.3172</v>
-      </c>
-      <c r="Q13" s="58">
-        <v>0.3172</v>
-      </c>
-      <c r="R13" s="107">
+        <v>0.31719999999999998</v>
+      </c>
+      <c r="Q13" s="40">
+        <v>0.31719999999999998</v>
+      </c>
+      <c r="R13" s="76">
         <f t="shared" si="2"/>
-        <v>2.2204</v>
-      </c>
-      <c r="S13" s="33"/>
-      <c r="T13" s="108"/>
-      <c r="U13" s="112"/>
-    </row>
-    <row r="14" ht="15.75" spans="1:21">
-      <c r="A14" s="8">
+        <v>2.2203999999999997</v>
+      </c>
+      <c r="S13" s="24"/>
+      <c r="T13" s="77"/>
+      <c r="U13" s="81"/>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="155" t="s">
+      <c r="B14" s="164"/>
+      <c r="C14" s="124" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="125" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="156" t="s">
+      <c r="F14" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="157" t="s">
+      <c r="G14" s="126" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="156" t="s">
+      <c r="H14" s="128" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="157" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="159" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="159" t="s">
+      <c r="I14" s="128" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="158" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="29">
+      <c r="J14" s="127" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14" s="21">
         <v>20</v>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="49">
         <v>1</v>
       </c>
-      <c r="M14" s="29">
+      <c r="M14" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="160" t="s">
+      <c r="N14" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="O14" s="73">
-        <v>0.0266</v>
-      </c>
-      <c r="P14" s="68">
+      <c r="O14" s="50">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="P14" s="47">
         <f t="shared" si="1"/>
-        <v>0.0266</v>
-      </c>
-      <c r="Q14" s="68">
-        <v>0.0266</v>
-      </c>
-      <c r="R14" s="115">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="Q14" s="47">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="R14" s="84">
         <f t="shared" si="2"/>
-        <v>0.532</v>
-      </c>
-      <c r="S14" s="117"/>
-      <c r="T14" s="116"/>
-      <c r="U14" s="112"/>
-    </row>
-    <row r="15" ht="15.75" spans="1:21">
-      <c r="A15" s="8">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="S14" s="86"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="81"/>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="134" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="165" t="s">
+      <c r="E15" s="135" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="166" t="s">
+      <c r="F15" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="166" t="s">
+      <c r="G15" s="136" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="166" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="167" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="167" t="s">
+      <c r="H15" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="166" t="s">
+      <c r="I15" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="167" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" s="37">
+      <c r="J15" s="136" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="26">
         <v>7</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="26">
         <v>1</v>
       </c>
-      <c r="M15" s="74">
+      <c r="M15" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N15" s="168" t="s">
+      <c r="N15" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="O15" s="76">
+      <c r="O15" s="52">
         <v>0.2127</v>
       </c>
-      <c r="P15" s="77">
+      <c r="P15" s="53">
         <f t="shared" si="1"/>
         <v>0.2127</v>
       </c>
-      <c r="Q15" s="77">
+      <c r="Q15" s="53">
         <v>0.2127</v>
       </c>
-      <c r="R15" s="118">
+      <c r="R15" s="87">
         <f t="shared" si="2"/>
-        <v>1.4889</v>
-      </c>
-      <c r="S15" s="119"/>
-      <c r="T15" s="120">
+        <v>1.4889000000000001</v>
+      </c>
+      <c r="S15" s="88"/>
+      <c r="T15" s="89">
         <v>0.189</v>
       </c>
-      <c r="U15" s="112"/>
-    </row>
-    <row r="16" ht="15.75" spans="1:21">
-      <c r="A16" s="8">
+      <c r="U15" s="81"/>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="138" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="139" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="169" t="s">
+      <c r="E16" s="139" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="170" t="s">
+      <c r="G16" s="139" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="170" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="170" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="170" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="170" t="s">
-        <v>97</v>
-      </c>
-      <c r="K16" s="39">
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="139" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="27">
         <v>7</v>
       </c>
-      <c r="L16" s="39">
+      <c r="L16" s="27">
         <v>1</v>
       </c>
-      <c r="M16" s="78">
+      <c r="M16" s="54">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N16" s="79" t="s">
+      <c r="N16" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" s="56">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="P16" s="57">
+        <f t="shared" si="1"/>
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="Q16" s="57">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="R16" s="90">
+        <f t="shared" si="2"/>
+        <v>6.8389999999999995</v>
+      </c>
+      <c r="S16" s="27"/>
+      <c r="T16" s="91">
+        <v>2.54</v>
+      </c>
+      <c r="U16" s="81"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="162" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="140" t="s">
         <v>115</v>
       </c>
-      <c r="O16" s="80">
-        <v>0.977</v>
-      </c>
-      <c r="P16" s="81">
-        <f t="shared" si="1"/>
-        <v>0.977</v>
-      </c>
-      <c r="Q16" s="81">
-        <v>0.977</v>
-      </c>
-      <c r="R16" s="121">
-        <f t="shared" si="2"/>
-        <v>6.839</v>
-      </c>
-      <c r="S16" s="39"/>
-      <c r="T16" s="122">
-        <v>2.54</v>
-      </c>
-      <c r="U16" s="112"/>
-    </row>
-    <row r="17" ht="15.75" spans="1:21">
-      <c r="A17" s="8">
-        <v>15</v>
-      </c>
-      <c r="B17" s="9" t="s">
+      <c r="D17" s="112" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="171" t="s">
+      <c r="E17" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="143" t="s">
+      <c r="F17" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="143" t="s">
+      <c r="G17" s="113" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="143" t="s">
+      <c r="I17" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="144" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="143" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="K17" s="13">
+      <c r="K17" s="10">
         <v>100</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="10">
         <v>2</v>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N17" s="172" t="s">
+      <c r="N17" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="O17" s="83">
-        <v>0.0014</v>
-      </c>
-      <c r="P17" s="58">
+      <c r="O17" s="58">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P17" s="40">
         <f t="shared" si="1"/>
-        <v>0.0028</v>
-      </c>
-      <c r="Q17" s="58">
-        <v>0.0014</v>
-      </c>
-      <c r="R17" s="107">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q17" s="40">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R17" s="76">
         <f t="shared" si="2"/>
-        <v>0.14</v>
-      </c>
-      <c r="S17" s="13"/>
-      <c r="T17" s="108"/>
-      <c r="U17" s="112"/>
-    </row>
-    <row r="18" ht="15.75" spans="1:21">
-      <c r="A18" s="8">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S17" s="10"/>
+      <c r="T17" s="77"/>
+      <c r="U17" s="81"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="173" t="s">
+      <c r="B18" s="163"/>
+      <c r="C18" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="115" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="115" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="G18" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="146" t="s">
+      <c r="I18" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="G18" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="146" t="s">
-        <v>127</v>
-      </c>
-      <c r="K18" s="17">
+      <c r="K18" s="13">
         <v>100</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="13">
         <v>2</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N18" s="174" t="s">
+      <c r="N18" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O18" s="85">
-        <v>0.0014</v>
-      </c>
-      <c r="P18" s="60">
+      <c r="O18" s="59">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P18" s="42">
         <f t="shared" si="1"/>
-        <v>0.0028</v>
-      </c>
-      <c r="Q18" s="60">
-        <v>0.0014</v>
-      </c>
-      <c r="R18" s="109">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q18" s="42">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R18" s="78">
         <f t="shared" si="2"/>
-        <v>0.14</v>
-      </c>
-      <c r="S18" s="17"/>
-      <c r="T18" s="110"/>
-      <c r="U18" s="112"/>
-    </row>
-    <row r="19" ht="15.75" spans="1:21">
-      <c r="A19" s="8">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S18" s="13"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="81"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="173" t="s">
+      <c r="B19" s="163"/>
+      <c r="C19" s="142" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="115" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="115" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="G19" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="146" t="s">
+      <c r="I19" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G19" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="I19" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="146" t="s">
-        <v>132</v>
-      </c>
-      <c r="K19" s="17">
+      <c r="K19" s="13">
         <v>100</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="13">
         <v>3</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N19" s="174" t="s">
+      <c r="N19" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O19" s="85">
-        <v>0.0014</v>
-      </c>
-      <c r="P19" s="60">
+      <c r="O19" s="59">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P19" s="42">
         <f t="shared" si="1"/>
-        <v>0.0042</v>
-      </c>
-      <c r="Q19" s="60">
-        <v>0.0014</v>
-      </c>
-      <c r="R19" s="109">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Q19" s="42">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R19" s="78">
         <f t="shared" si="2"/>
-        <v>0.14</v>
-      </c>
-      <c r="S19" s="17"/>
-      <c r="T19" s="110"/>
-      <c r="U19" s="112"/>
-    </row>
-    <row r="20" ht="15.75" spans="1:21">
-      <c r="A20" s="8">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S19" s="13"/>
+      <c r="T19" s="79"/>
+      <c r="U19" s="81"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="173" t="s">
+      <c r="B20" s="163"/>
+      <c r="C20" s="142" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="115" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="146" t="s">
+      <c r="F20" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="146" t="s">
+      <c r="G20" s="117" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="146" t="s">
+      <c r="H20" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="148" t="s">
+      <c r="I20" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="115" t="s">
         <v>137</v>
       </c>
-      <c r="H20" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="146" t="s">
-        <v>139</v>
-      </c>
-      <c r="K20" s="17">
+      <c r="K20" s="13">
         <v>20</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="13">
         <v>2</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N20" s="174" t="s">
+      <c r="N20" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O20" s="86">
-        <v>0.0295</v>
-      </c>
-      <c r="P20" s="60">
+      <c r="O20" s="60">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="P20" s="42">
         <f t="shared" si="1"/>
-        <v>0.059</v>
-      </c>
-      <c r="Q20" s="60">
-        <v>0.0295</v>
-      </c>
-      <c r="R20" s="109">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="Q20" s="42">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="R20" s="78">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S20" s="17"/>
-      <c r="T20" s="110"/>
-      <c r="U20" s="112"/>
-    </row>
-    <row r="21" ht="15.75" spans="1:21">
-      <c r="A21" s="8">
+      <c r="S20" s="13"/>
+      <c r="T20" s="79"/>
+      <c r="U20" s="81"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="173" t="s">
+      <c r="B21" s="163"/>
+      <c r="C21" s="142" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="115" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="115" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="146" t="s">
+      <c r="G21" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="146" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="149" t="s">
+      <c r="H21" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="148" t="s">
+      <c r="I21" s="117" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="J21" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="I21" s="148" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="146" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" s="17">
+      <c r="K21" s="13">
         <v>10</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="13">
         <v>1</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N21" s="174" t="s">
+      <c r="N21" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O21" s="85">
+      <c r="O21" s="59">
         <v>0.1133</v>
       </c>
-      <c r="P21" s="60">
+      <c r="P21" s="42">
         <f t="shared" si="1"/>
         <v>0.1133</v>
       </c>
-      <c r="Q21" s="60">
+      <c r="Q21" s="42">
         <v>0.1133</v>
       </c>
-      <c r="R21" s="109">
+      <c r="R21" s="78">
         <f t="shared" si="2"/>
         <v>1.133</v>
       </c>
-      <c r="S21" s="17"/>
-      <c r="T21" s="110"/>
-      <c r="U21" s="112"/>
-    </row>
-    <row r="22" ht="15.75" spans="1:21">
-      <c r="A22" s="8">
+      <c r="S21" s="13"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="81"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="173" t="s">
+      <c r="B22" s="163"/>
+      <c r="C22" s="142" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="115" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="115" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="115" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="146" t="s">
+      <c r="G22" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="146" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="146" t="s">
+      <c r="H22" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G22" s="148" t="s">
+      <c r="I22" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="I22" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="146" t="s">
-        <v>152</v>
-      </c>
-      <c r="K22" s="17">
+      <c r="K22" s="13">
         <v>100</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="13">
         <v>1</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N22" s="174" t="s">
+      <c r="N22" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O22" s="85">
-        <v>0.0028</v>
-      </c>
-      <c r="P22" s="60">
+      <c r="O22" s="59">
+        <v>2.8E-3</v>
+      </c>
+      <c r="P22" s="42">
         <f t="shared" si="1"/>
-        <v>0.0028</v>
-      </c>
-      <c r="Q22" s="60">
-        <v>0.0028</v>
-      </c>
-      <c r="R22" s="109">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q22" s="42">
+        <v>2.8E-3</v>
+      </c>
+      <c r="R22" s="78">
         <f t="shared" si="2"/>
-        <v>0.28</v>
-      </c>
-      <c r="S22" s="17"/>
-      <c r="T22" s="110"/>
-      <c r="U22" s="112"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="15.75" spans="1:21">
-      <c r="A23" s="8">
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="S22" s="13"/>
+      <c r="T22" s="79"/>
+      <c r="U22" s="81"/>
+    </row>
+    <row r="23" spans="1:21" s="1" customFormat="1">
+      <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="175" t="s">
+      <c r="B23" s="164"/>
+      <c r="C23" s="144" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="125" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="125" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="G23" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="156" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="156" t="s">
+      <c r="I23" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="125" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="159" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="156" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="156" t="s">
-        <v>157</v>
-      </c>
-      <c r="K23" s="28">
+      <c r="K23" s="20">
         <v>100</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="23">
         <v>8</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="21">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N23" s="87" t="s">
+      <c r="N23" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="73">
-        <v>0.0018</v>
-      </c>
-      <c r="P23" s="68">
+      <c r="O23" s="50">
+        <v>1.8E-3</v>
+      </c>
+      <c r="P23" s="47">
         <f t="shared" si="1"/>
-        <v>0.0144</v>
-      </c>
-      <c r="Q23" s="68">
-        <v>0.0018</v>
-      </c>
-      <c r="R23" s="115">
+        <v>1.44E-2</v>
+      </c>
+      <c r="Q23" s="47">
+        <v>1.8E-3</v>
+      </c>
+      <c r="R23" s="84">
         <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
-      <c r="S23" s="28"/>
-      <c r="T23" s="116"/>
-      <c r="U23" s="123"/>
-    </row>
-    <row r="24" ht="15.75" spans="1:21">
-      <c r="A24" s="8">
+      <c r="S23" s="20"/>
+      <c r="T23" s="85"/>
+      <c r="U23" s="92"/>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="162" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="145" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="146" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="176" t="s">
+      <c r="E24" s="146" t="s">
         <v>159</v>
       </c>
-      <c r="D24" s="177" t="s">
+      <c r="F24" s="146" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="177" t="s">
+      <c r="G24" s="147" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="177" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="178" t="s">
-        <v>163</v>
-      </c>
-      <c r="H24" s="178" t="s">
+      <c r="H24" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="177" t="s">
+      <c r="I24" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="178" t="s">
-        <v>97</v>
-      </c>
-      <c r="K24" s="45">
+      <c r="J24" s="147" t="s">
+        <v>95</v>
+      </c>
+      <c r="K24" s="30">
         <v>10</v>
       </c>
-      <c r="L24" s="45">
+      <c r="L24" s="30">
         <v>1</v>
       </c>
-      <c r="M24" s="44">
+      <c r="M24" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="88" t="s">
-        <v>164</v>
-      </c>
-      <c r="O24" s="89">
+      <c r="N24" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="O24" s="63">
         <v>1.2</v>
       </c>
-      <c r="P24" s="89">
+      <c r="P24" s="63">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="Q24" s="89">
+      <c r="Q24" s="63">
         <v>1.2</v>
       </c>
-      <c r="R24" s="124">
+      <c r="R24" s="93">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="S24" s="125" t="s">
+      <c r="S24" s="94" t="s">
+        <v>163</v>
+      </c>
+      <c r="T24" s="95">
+        <v>4.7619999999999996</v>
+      </c>
+      <c r="U24" s="81"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="163"/>
+      <c r="C25" s="142" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="T24" s="126">
-        <v>4.762</v>
-      </c>
-      <c r="U24" s="112"/>
-    </row>
-    <row r="25" ht="15.75" spans="1:21">
-      <c r="A25" s="8">
-        <v>23</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="173" t="s">
+      <c r="E25" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="146" t="s">
+      <c r="F25" s="115" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="146" t="s">
+      <c r="G25" s="117" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="146" t="s">
+      <c r="H25" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="148" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="146" t="s">
+      <c r="I25" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="J25" s="148" t="s">
-        <v>97</v>
-      </c>
-      <c r="K25" s="25">
+      <c r="J25" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="K25" s="19">
         <v>6</v>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="19">
         <v>1</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N25" s="174" t="s">
+      <c r="N25" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="O25" s="85">
-        <v>0.278</v>
-      </c>
-      <c r="P25" s="60">
+      <c r="O25" s="59">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="P25" s="42">
         <f t="shared" si="1"/>
-        <v>0.278</v>
-      </c>
-      <c r="Q25" s="60">
-        <v>0.278</v>
-      </c>
-      <c r="R25" s="109">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="Q25" s="42">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="R25" s="78">
         <f t="shared" si="2"/>
-        <v>1.668</v>
-      </c>
-      <c r="S25" s="17"/>
-      <c r="T25" s="110"/>
-      <c r="U25" s="112"/>
-    </row>
-    <row r="26" ht="15.75" spans="1:21">
-      <c r="A26" s="8">
+        <v>1.6680000000000001</v>
+      </c>
+      <c r="S25" s="13"/>
+      <c r="T25" s="79"/>
+      <c r="U25" s="81"/>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="175" t="s">
+      <c r="B26" s="164"/>
+      <c r="C26" s="144" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="125" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="125" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="156" t="s">
+      <c r="F26" s="125" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="156" t="s">
+      <c r="G26" s="128" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="156" t="s">
+      <c r="H26" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G26" s="159" t="s">
+      <c r="I26" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="128" t="s">
         <v>176</v>
       </c>
-      <c r="H26" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="156" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="159" t="s">
-        <v>178</v>
-      </c>
-      <c r="K26" s="31">
+      <c r="K26" s="23">
         <v>6</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="23">
         <v>1</v>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N26" s="179" t="s">
+      <c r="N26" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="O26" s="73">
-        <v>0.1698</v>
-      </c>
-      <c r="P26" s="68">
+      <c r="O26" s="50">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="P26" s="47">
         <f t="shared" si="1"/>
-        <v>0.1698</v>
-      </c>
-      <c r="Q26" s="68">
-        <v>0.1698</v>
-      </c>
-      <c r="R26" s="115">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="Q26" s="47">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>1.0188</v>
-      </c>
-      <c r="S26" s="117"/>
-      <c r="T26" s="116"/>
-      <c r="U26" s="112"/>
-    </row>
-    <row r="27" ht="15.75" spans="1:21">
-      <c r="A27" s="8">
+        <v>1.0188000000000001</v>
+      </c>
+      <c r="S26" s="86"/>
+      <c r="T26" s="85"/>
+      <c r="U26" s="81"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="162" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="145" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" s="146" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="176" t="s">
+      <c r="E27" s="146" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="177" t="s">
+      <c r="F27" s="146" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="146" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="177" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="177" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27" s="177" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="177" t="s">
+      <c r="H27" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="177" t="s">
+      <c r="I27" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="J27" s="177" t="s">
-        <v>97</v>
-      </c>
-      <c r="K27" s="44">
+      <c r="J27" s="146" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="29">
         <v>100</v>
       </c>
-      <c r="L27" s="44">
+      <c r="L27" s="29">
         <v>1</v>
       </c>
-      <c r="M27" s="44">
+      <c r="M27" s="29">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N27" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="O27" s="89">
+      <c r="N27" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="O27" s="63">
         <v>36.9</v>
       </c>
-      <c r="P27" s="89">
+      <c r="P27" s="63">
         <f t="shared" si="1"/>
         <v>36.9</v>
       </c>
-      <c r="Q27" s="89">
-        <v>0.369</v>
-      </c>
-      <c r="R27" s="124">
+      <c r="Q27" s="63">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="R27" s="93">
         <f t="shared" si="2"/>
         <v>36.9</v>
       </c>
-      <c r="S27" s="127" t="s">
+      <c r="S27" s="96" t="s">
+        <v>183</v>
+      </c>
+      <c r="T27" s="95"/>
+      <c r="U27" s="81"/>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="6">
+        <v>26</v>
+      </c>
+      <c r="B28" s="163"/>
+      <c r="C28" s="149" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="150" t="s">
         <v>185</v>
       </c>
-      <c r="T27" s="126"/>
-      <c r="U27" s="112"/>
-    </row>
-    <row r="28" ht="15.75" spans="1:21">
-      <c r="A28" s="8">
-        <v>26</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="180" t="s">
+      <c r="E28" s="150" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="150" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="181" t="s">
+      <c r="G28" s="150" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="181" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="181" t="s">
+      <c r="H28" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="151" t="s">
         <v>188</v>
       </c>
-      <c r="G28" s="181" t="s">
-        <v>189</v>
-      </c>
-      <c r="H28" s="181" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="181" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="182" t="s">
-        <v>190</v>
-      </c>
-      <c r="K28" s="92">
+      <c r="K28" s="65">
         <v>12</v>
       </c>
-      <c r="L28" s="47">
+      <c r="L28" s="31">
         <v>2</v>
       </c>
-      <c r="M28" s="47">
+      <c r="M28" s="31">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28" s="93" t="s">
-        <v>191</v>
-      </c>
-      <c r="O28" s="94">
+      <c r="N28" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="O28" s="67">
         <v>0.75</v>
       </c>
-      <c r="P28" s="95">
+      <c r="P28" s="68">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="Q28" s="94">
+      <c r="Q28" s="67">
         <v>0.75</v>
       </c>
-      <c r="R28" s="96">
+      <c r="R28" s="69">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="S28" s="128"/>
-      <c r="T28" s="129"/>
-      <c r="U28" s="112"/>
-    </row>
-    <row r="29" ht="15.75" spans="1:21">
-      <c r="A29" s="8">
+      <c r="S28" s="97"/>
+      <c r="T28" s="98"/>
+      <c r="U28" s="81"/>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="180" t="s">
+      <c r="B29" s="163"/>
+      <c r="C29" s="149" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="150" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="150" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="150" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="181" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" s="181" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="181" t="s">
-        <v>194</v>
-      </c>
-      <c r="G29" s="181" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" s="181" t="s">
+      <c r="G29" s="150" t="s">
+        <v>181</v>
+      </c>
+      <c r="H29" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="181" t="s">
+      <c r="I29" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="182" t="s">
-        <v>97</v>
-      </c>
-      <c r="K29" s="92">
+      <c r="J29" s="151" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="65">
         <v>10</v>
       </c>
-      <c r="L29" s="47">
+      <c r="L29" s="31">
         <v>1</v>
       </c>
-      <c r="M29" s="47">
+      <c r="M29" s="31">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N29" s="93" t="s">
-        <v>184</v>
-      </c>
-      <c r="O29" s="96">
-        <v>0.553</v>
-      </c>
-      <c r="P29" s="95">
+      <c r="N29" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="O29" s="69">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="P29" s="68">
         <f t="shared" si="1"/>
-        <v>0.553</v>
-      </c>
-      <c r="Q29" s="95">
-        <v>0.553</v>
-      </c>
-      <c r="R29" s="96">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Q29" s="68">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="R29" s="69">
         <f t="shared" si="2"/>
         <v>5.53</v>
       </c>
-      <c r="S29" s="128"/>
-      <c r="T29" s="129"/>
-      <c r="U29" s="112"/>
-    </row>
-    <row r="30" ht="15.75" spans="1:21">
-      <c r="A30" s="8">
+      <c r="S29" s="97"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="81"/>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="41" t="s">
+      <c r="B30" s="163"/>
+      <c r="C30" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="115" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="115" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="115" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="146" t="s">
+      <c r="G30" s="115" t="s">
         <v>196</v>
       </c>
-      <c r="E30" s="146" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="146" t="s">
-        <v>197</v>
-      </c>
-      <c r="G30" s="146" t="s">
-        <v>198</v>
-      </c>
-      <c r="H30" s="146" t="s">
-        <v>197</v>
-      </c>
-      <c r="I30" s="146" t="s">
+      <c r="H30" s="115" t="s">
+        <v>195</v>
+      </c>
+      <c r="I30" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="148" t="s">
-        <v>190</v>
-      </c>
-      <c r="K30" s="25">
+      <c r="J30" s="117" t="s">
+        <v>188</v>
+      </c>
+      <c r="K30" s="19">
         <v>20</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="13">
         <v>1</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="97" t="s">
+      <c r="N30" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="O30" s="98">
-        <v>0.0263</v>
-      </c>
-      <c r="P30" s="99">
+      <c r="O30" s="71">
+        <v>2.63E-2</v>
+      </c>
+      <c r="P30" s="72">
         <f>O30*L30</f>
-        <v>0.0263</v>
-      </c>
-      <c r="Q30" s="130">
-        <v>0.0263</v>
-      </c>
-      <c r="R30" s="131">
+        <v>2.63E-2</v>
+      </c>
+      <c r="Q30" s="99">
+        <v>2.63E-2</v>
+      </c>
+      <c r="R30" s="100">
         <f>Q30*K30</f>
-        <v>0.526</v>
-      </c>
-      <c r="S30" s="113"/>
-      <c r="T30" s="110"/>
-      <c r="U30" s="112"/>
-    </row>
-    <row r="31" ht="15.75" spans="1:21">
-      <c r="A31" s="8">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="S30" s="82"/>
+      <c r="T30" s="79"/>
+      <c r="U30" s="81"/>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="173" t="s">
+      <c r="B31" s="163"/>
+      <c r="C31" s="142" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="115" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="115" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="146" t="s">
+      <c r="F31" s="115" t="s">
         <v>200</v>
       </c>
-      <c r="E31" s="146" t="s">
+      <c r="G31" s="115" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="146" t="s">
+      <c r="H31" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="146" t="s">
-        <v>203</v>
-      </c>
-      <c r="H31" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="I31" s="146" t="s">
+      <c r="I31" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="J31" s="148" t="s">
-        <v>97</v>
-      </c>
-      <c r="K31" s="25">
+      <c r="J31" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="19">
         <v>15</v>
       </c>
-      <c r="L31" s="25">
+      <c r="L31" s="19">
         <v>2</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N31" s="183" t="s">
+      <c r="N31" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="85">
+      <c r="O31" s="59">
         <v>0.1085</v>
       </c>
-      <c r="P31" s="60">
+      <c r="P31" s="42">
         <f t="shared" si="1"/>
         <v>0.217</v>
       </c>
-      <c r="Q31" s="60">
+      <c r="Q31" s="42">
         <v>0.1085</v>
       </c>
-      <c r="R31" s="109">
+      <c r="R31" s="78">
         <f t="shared" si="2"/>
-        <v>1.6275</v>
-      </c>
-      <c r="S31" s="17"/>
-      <c r="T31" s="110"/>
-      <c r="U31" s="112"/>
-    </row>
-    <row r="32" ht="15.75" spans="1:21">
-      <c r="A32" s="8">
+        <v>1.6274999999999999</v>
+      </c>
+      <c r="S31" s="13"/>
+      <c r="T31" s="79"/>
+      <c r="U31" s="81"/>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="184" t="s">
+      <c r="B32" s="163"/>
+      <c r="C32" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" s="154" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="E32" s="185" t="s">
-        <v>207</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49">
+      <c r="F32" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32">
         <v>5</v>
       </c>
-      <c r="M32" s="23">
+      <c r="M32" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N32" s="49"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="101"/>
-      <c r="Q32" s="101"/>
-      <c r="R32" s="132"/>
-      <c r="S32" s="133" t="s">
+      <c r="N32" s="32"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="101"/>
+      <c r="S32" s="102" t="s">
+        <v>206</v>
+      </c>
+      <c r="T32" s="103"/>
+      <c r="U32" s="81"/>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" s="33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="164"/>
+      <c r="C33" s="155" t="s">
+        <v>207</v>
+      </c>
+      <c r="D33" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="T32" s="134"/>
-      <c r="U32" s="112"/>
-    </row>
-    <row r="33" ht="15.75" spans="1:21">
-      <c r="A33" s="50">
-        <v>31</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="186" t="s">
+      <c r="E33" s="156" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="187" t="s">
-        <v>211</v>
-      </c>
-      <c r="F33" s="52" t="s">
-        <v>211</v>
-      </c>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="52">
+      <c r="F33" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34">
         <v>5</v>
       </c>
-      <c r="M33" s="29">
+      <c r="M33" s="21">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N33" s="52"/>
-      <c r="O33" s="102"/>
-      <c r="P33" s="102"/>
-      <c r="Q33" s="102"/>
-      <c r="R33" s="135"/>
-      <c r="S33" s="136" t="s">
-        <v>208</v>
-      </c>
-      <c r="T33" s="137"/>
-      <c r="U33" s="112"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:21">
+      <c r="N33" s="34"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
+      <c r="Q33" s="74"/>
+      <c r="R33" s="104"/>
+      <c r="S33" s="105" t="s">
+        <v>206</v>
+      </c>
+      <c r="T33" s="106"/>
+      <c r="U33" s="81"/>
+    </row>
+    <row r="34" spans="1:21" ht="15.75">
       <c r="A34"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="103" t="s">
-        <v>212</v>
-      </c>
-      <c r="M34" s="103"/>
-      <c r="N34" s="103"/>
-      <c r="P34" s="104">
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="160" t="s">
+        <v>210</v>
+      </c>
+      <c r="M34" s="160"/>
+      <c r="N34" s="160"/>
+      <c r="P34" s="75">
         <f>SUM(P3:P31)</f>
-        <v>43.3427</v>
-      </c>
-      <c r="R34" s="138">
+        <v>43.342699999999994</v>
+      </c>
+      <c r="R34" s="107">
         <f>SUM(R3:R31)</f>
-        <v>89.3528</v>
-      </c>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="112"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:21">
+        <v>89.352799999999988</v>
+      </c>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="81"/>
+    </row>
+    <row r="35" spans="1:21" ht="15.75">
       <c r="A35"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="105" t="s">
-        <v>213</v>
-      </c>
-      <c r="M35" s="105"/>
-      <c r="N35" s="105"/>
-      <c r="R35" s="139">
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="161" t="s">
+        <v>211</v>
+      </c>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="R35" s="108">
         <f>R34/5</f>
-        <v>17.87056</v>
-      </c>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="112"/>
+        <v>17.870559999999998</v>
+      </c>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="81"/>
     </row>
     <row r="36" spans="1:21">
       <c r="A36"/>
-      <c r="T36" s="112"/>
-      <c r="U36" s="112"/>
+      <c r="T36" s="81"/>
+      <c r="U36" s="81"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37"/>
-      <c r="T37" s="112"/>
-      <c r="U37" s="112"/>
+      <c r="T37" s="81"/>
+      <c r="U37" s="81"/>
     </row>
     <row r="38" spans="1:21">
       <c r="A38"/>
-      <c r="T38" s="112"/>
-      <c r="U38" s="112"/>
+      <c r="T38" s="81"/>
+      <c r="U38" s="81"/>
     </row>
     <row r="39" spans="1:21">
       <c r="A39"/>
-      <c r="T39" s="112"/>
-      <c r="U39" s="112"/>
+      <c r="T39" s="81"/>
+      <c r="U39" s="81"/>
     </row>
     <row r="40" spans="1:21">
       <c r="A40"/>
-      <c r="T40" s="112"/>
-      <c r="U40" s="112"/>
+      <c r="T40" s="81"/>
+      <c r="U40" s="81"/>
     </row>
     <row r="41" spans="1:21">
       <c r="A41"/>
-      <c r="T41" s="112"/>
-      <c r="U41" s="112"/>
+      <c r="T41" s="81"/>
+      <c r="U41" s="81"/>
     </row>
     <row r="42" spans="1:21">
       <c r="A42"/>
-      <c r="T42" s="112"/>
-      <c r="U42" s="112"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:21">
+      <c r="T42" s="81"/>
+      <c r="U42" s="81"/>
+    </row>
+    <row r="43" spans="1:21" ht="15.75" customHeight="1">
       <c r="A43"/>
-      <c r="T43" s="112"/>
-      <c r="U43" s="112"/>
+      <c r="T43" s="81"/>
+      <c r="U43" s="81"/>
     </row>
     <row r="44" spans="1:21">
       <c r="A44"/>
-      <c r="T44" s="112"/>
-      <c r="U44" s="112"/>
+      <c r="T44" s="81"/>
+      <c r="U44" s="81"/>
     </row>
     <row r="45" spans="1:21">
       <c r="A45"/>
-      <c r="T45" s="112"/>
-      <c r="U45" s="112"/>
+      <c r="T45" s="81"/>
+      <c r="U45" s="81"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46"/>
-      <c r="T46" s="112"/>
-      <c r="U46" s="112"/>
+      <c r="T46" s="81"/>
+      <c r="U46" s="81"/>
     </row>
     <row r="47" spans="1:21">
       <c r="A47"/>
-      <c r="T47" s="112"/>
-      <c r="U47" s="112"/>
+      <c r="T47" s="81"/>
+      <c r="U47" s="81"/>
     </row>
     <row r="48" spans="1:21">
       <c r="A48"/>
-      <c r="T48" s="112"/>
-      <c r="U48" s="112"/>
+      <c r="T48" s="81"/>
+      <c r="U48" s="81"/>
     </row>
     <row r="49" spans="8:19">
-      <c r="H49" s="54"/>
-      <c r="S49" s="140"/>
+      <c r="H49" s="36"/>
+      <c r="S49" s="109"/>
     </row>
     <row r="50" spans="8:19">
-      <c r="H50" s="54"/>
-      <c r="S50" s="140"/>
+      <c r="H50" s="36"/>
+      <c r="S50" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4804,7 +4138,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91b8d679-ff0b-4b19-a610-6c243faf4003}</x14:id>
+          <x14:id>{91B8D679-FF0B-4B19-A610-6C243FAF4003}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4818,7 +4152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8602b36a-2b77-4657-823a-0d7b51a8c0d4}</x14:id>
+          <x14:id>{8602B36A-2B77-4657-823A-0D7B51A8C0D4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4832,7 +4166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f78c7e8a-5679-42c3-8c50-13119118a4a2}</x14:id>
+          <x14:id>{F78C7E8A-5679-42C3-8C50-13119118A4A2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4846,7 +4180,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c28e1de-fd45-4e1a-bdb3-0d57d1810c06}</x14:id>
+          <x14:id>{4C28E1DE-FD45-4E1A-BDB3-0D57D1810C06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4894,7 +4228,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea91e7cb-e035-4d5f-bd6b-48dfb63ccbdb}</x14:id>
+          <x14:id>{EA91E7CB-E035-4D5F-BD6B-48DFB63CCBDB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4930,7 +4264,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72f02937-73f0-4b31-b5ca-2d756df15d65}</x14:id>
+          <x14:id>{72F02937-73F0-4B31-B5CA-2D756DF15D65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4944,7 +4278,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54c4f5f8-ede7-4601-aeac-8e612bf30c27}</x14:id>
+          <x14:id>{54C4F5F8-EDE7-4601-AEAC-8E612BF30C27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4970,7 +4304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94e20060-874b-439f-8fda-33b3dd39ffe6}</x14:id>
+          <x14:id>{94E20060-874B-439F-8FDA-33B3DD39FFE6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4984,7 +4318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbb933a5-5d45-42ae-8d8b-f05439ef033d}</x14:id>
+          <x14:id>{DBB933A5-5D45-42AE-8D8B-F05439EF033D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4998,7 +4332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ffb8fd96-bb87-47dd-9e3b-fba7e127703c}</x14:id>
+          <x14:id>{FFB8FD96-BB87-47DD-9E3B-FBA7E127703C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5012,7 +4346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc4f43e8-ca2d-4f5a-a416-ccdf4c097d17}</x14:id>
+          <x14:id>{DC4F43E8-CA2D-4F5A-A416-CCDF4C097D17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5042,42 +4376,41 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N8" r:id="rId1" display="LCSC"/>
-    <hyperlink ref="N9" r:id="rId2" display="LCSC"/>
-    <hyperlink ref="N10" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="N11" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="N12" r:id="rId5" display="LCSC"/>
-    <hyperlink ref="N13" r:id="rId6" display="LCSC"/>
-    <hyperlink ref="N14" r:id="rId7" display="LCSC"/>
-    <hyperlink ref="N17" r:id="rId8" display="LCSC"/>
-    <hyperlink ref="N18" r:id="rId9" display="LCSC"/>
-    <hyperlink ref="N19" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="N20" r:id="rId11" display="LCSC"/>
-    <hyperlink ref="N22" r:id="rId12" display="LCSC"/>
-    <hyperlink ref="N23" r:id="rId13" display="LCSC"/>
-    <hyperlink ref="N25" r:id="rId14" display="LCSC"/>
-    <hyperlink ref="N26" r:id="rId15" display="LCSC"/>
-    <hyperlink ref="N31" r:id="rId16" display="LCSC"/>
-    <hyperlink ref="N6" r:id="rId17" display="LCSC"/>
-    <hyperlink ref="N7" r:id="rId18" display="LCSC"/>
-    <hyperlink ref="N21" r:id="rId19" display="LCSC"/>
-    <hyperlink ref="N24" r:id="rId20" display="Alibaba"/>
-    <hyperlink ref="N3" r:id="rId21" display="LCSC"/>
-    <hyperlink ref="N4" r:id="rId22" display="LCSC"/>
-    <hyperlink ref="N5" r:id="rId23" display="LCSC"/>
-    <hyperlink ref="N27" r:id="rId24" display="Aliexpress"/>
-    <hyperlink ref="N29" r:id="rId25" display="Aliexpress"/>
-    <hyperlink ref="N15" r:id="rId26" display="LCSC"/>
-    <hyperlink ref="N30" r:id="rId27" display="LCSC"/>
+    <hyperlink ref="N8" r:id="rId1"/>
+    <hyperlink ref="N9" r:id="rId2"/>
+    <hyperlink ref="N10" r:id="rId3"/>
+    <hyperlink ref="N11" r:id="rId4"/>
+    <hyperlink ref="N12" r:id="rId5"/>
+    <hyperlink ref="N13" r:id="rId6"/>
+    <hyperlink ref="N14" r:id="rId7"/>
+    <hyperlink ref="N17" r:id="rId8"/>
+    <hyperlink ref="N18" r:id="rId9"/>
+    <hyperlink ref="N19" r:id="rId10"/>
+    <hyperlink ref="N20" r:id="rId11"/>
+    <hyperlink ref="N22" r:id="rId12"/>
+    <hyperlink ref="N23" r:id="rId13"/>
+    <hyperlink ref="N25" r:id="rId14"/>
+    <hyperlink ref="N26" r:id="rId15"/>
+    <hyperlink ref="N31" r:id="rId16"/>
+    <hyperlink ref="N6" r:id="rId17"/>
+    <hyperlink ref="N7" r:id="rId18"/>
+    <hyperlink ref="N21" r:id="rId19"/>
+    <hyperlink ref="N24" r:id="rId20"/>
+    <hyperlink ref="N3" r:id="rId21"/>
+    <hyperlink ref="N4" r:id="rId22"/>
+    <hyperlink ref="N5" r:id="rId23"/>
+    <hyperlink ref="N27" r:id="rId24"/>
+    <hyperlink ref="N29" r:id="rId25"/>
+    <hyperlink ref="N15" r:id="rId26"/>
+    <hyperlink ref="N30" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91b8d679-ff0b-4b19-a610-6c243faf4003}">
+          <x14:cfRule type="dataBar" id="{91B8D679-FF0B-4B19-A610-6C243FAF4003}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5090,7 +4423,7 @@
           <xm:sqref>S11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8602b36a-2b77-4657-823a-0d7b51a8c0d4}">
+          <x14:cfRule type="dataBar" id="{8602B36A-2B77-4657-823A-0D7B51A8C0D4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5103,7 +4436,7 @@
           <xm:sqref>S15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f78c7e8a-5679-42c3-8c50-13119118a4a2}">
+          <x14:cfRule type="dataBar" id="{F78C7E8A-5679-42C3-8C50-13119118A4A2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5116,7 +4449,7 @@
           <xm:sqref>N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c28e1de-fd45-4e1a-bdb3-0d57d1810c06}">
+          <x14:cfRule type="dataBar" id="{4C28E1DE-FD45-4E1A-BDB3-0D57D1810C06}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5129,7 +4462,7 @@
           <xm:sqref>S24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea91e7cb-e035-4d5f-bd6b-48dfb63ccbdb}">
+          <x14:cfRule type="dataBar" id="{EA91E7CB-E035-4D5F-BD6B-48DFB63CCBDB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5142,7 +4475,7 @@
           <xm:sqref>S32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72f02937-73f0-4b31-b5ca-2d756df15d65}">
+          <x14:cfRule type="dataBar" id="{72F02937-73F0-4B31-B5CA-2D756DF15D65}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5155,7 +4488,7 @@
           <xm:sqref>S33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{54c4f5f8-ede7-4601-aeac-8e612bf30c27}">
+          <x14:cfRule type="dataBar" id="{54C4F5F8-EDE7-4601-AEAC-8E612BF30C27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5168,7 +4501,7 @@
           <xm:sqref>R35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94e20060-874b-439f-8fda-33b3dd39ffe6}">
+          <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5181,7 +4514,7 @@
           <xm:sqref>N3:N4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbb933a5-5d45-42ae-8d8b-f05439ef033d}">
+          <x14:cfRule type="dataBar" id="{DBB933A5-5D45-42AE-8D8B-F05439EF033D}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5194,7 +4527,7 @@
           <xm:sqref>N23:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ffb8fd96-bb87-47dd-9e3b-fba7e127703c}">
+          <x14:cfRule type="dataBar" id="{FFB8FD96-BB87-47DD-9E3B-FBA7E127703C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5207,7 +4540,7 @@
           <xm:sqref>R3:R33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc4f43e8-ca2d-4f5a-a416-ccdf4c097d17}">
+          <x14:cfRule type="dataBar" id="{DC4F43E8-CA2D-4F5A-A416-CCDF4C097D17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
